--- a/zakljucni_list_excel.xlsx
+++ b/zakljucni_list_excel.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="423">
   <si>
     <t>ZAKLJUČNI LIST</t>
   </si>
   <si>
-    <t>za period: 01.01.2024. do 20.05.2024.</t>
+    <t>za period: 01.01.2025. do 18.09.2025.</t>
   </si>
   <si>
     <t>Početno stanje</t>
@@ -70,24 +70,6 @@
     <t>Oprema</t>
   </si>
   <si>
-    <t>011210</t>
-  </si>
-  <si>
-    <t>Oprema za saobraćaj</t>
-  </si>
-  <si>
-    <t>011211</t>
-  </si>
-  <si>
-    <t>Oprema za kopneni saobraćaj</t>
-  </si>
-  <si>
-    <t>011219</t>
-  </si>
-  <si>
-    <t>Ispravka vrednosti saobraćajne opreme</t>
-  </si>
-  <si>
     <t>011220</t>
   </si>
   <si>
@@ -130,6 +112,30 @@
     <t>Ispravka vrednosti administrativne opreme</t>
   </si>
   <si>
+    <t>015000</t>
+  </si>
+  <si>
+    <t>NEFINANSIJSKA IMOVINA U PRIPREMI I AVANSI</t>
+  </si>
+  <si>
+    <t>015100</t>
+  </si>
+  <si>
+    <t>Nefinansijska imovina u pripremi</t>
+  </si>
+  <si>
+    <t>015120</t>
+  </si>
+  <si>
+    <t>Oprema u pripremi</t>
+  </si>
+  <si>
+    <t>015122</t>
+  </si>
+  <si>
+    <t>Administrativna oprema u pripremi</t>
+  </si>
+  <si>
     <t>016000</t>
   </si>
   <si>
@@ -151,33 +157,6 @@
     <t>016121</t>
   </si>
   <si>
-    <t>020000</t>
-  </si>
-  <si>
-    <t>NEFINANSIJSKA IMOVINA U ZALIHAMA</t>
-  </si>
-  <si>
-    <t>022000</t>
-  </si>
-  <si>
-    <t>ZALIHE SITNOG INVENTARA I POTROŠNOG MATERIJALA</t>
-  </si>
-  <si>
-    <t>022100</t>
-  </si>
-  <si>
-    <t>Zalihe sitnog inventara</t>
-  </si>
-  <si>
-    <t>022120</t>
-  </si>
-  <si>
-    <t>Sitan inventar u upotrebi</t>
-  </si>
-  <si>
-    <t>022121</t>
-  </si>
-  <si>
     <t>100000</t>
   </si>
   <si>
@@ -460,6 +439,78 @@
     <t>234211</t>
   </si>
   <si>
+    <t>236000</t>
+  </si>
+  <si>
+    <t>OBAVEZE PO OSNOVU SOCIJALNE POMOĆI ZAPOSLENIMA</t>
+  </si>
+  <si>
+    <t>236100</t>
+  </si>
+  <si>
+    <t>Obaveze po osnovu neto isplata soc.pomoći zaposlenima</t>
+  </si>
+  <si>
+    <t>236120</t>
+  </si>
+  <si>
+    <t>Obaveze po osnovu neto naknada refundacije</t>
+  </si>
+  <si>
+    <t>236122</t>
+  </si>
+  <si>
+    <t>Obaveze po osnovu neto naknada za bolov.preko 30 dana</t>
+  </si>
+  <si>
+    <t>236200</t>
+  </si>
+  <si>
+    <t>Obaveze po osnovu poreza na socij.pomoć zaposlenima</t>
+  </si>
+  <si>
+    <t>236210</t>
+  </si>
+  <si>
+    <t>236211</t>
+  </si>
+  <si>
+    <t>236300</t>
+  </si>
+  <si>
+    <t>Obaveze po osnovu doprinosa za PIO za socij.pomoć zapos.</t>
+  </si>
+  <si>
+    <t>236310</t>
+  </si>
+  <si>
+    <t>236311</t>
+  </si>
+  <si>
+    <t>236400</t>
+  </si>
+  <si>
+    <t>Obaveze po osnovu dopr. za zdrav.osig. za socij.pomoć zapos.</t>
+  </si>
+  <si>
+    <t>236410</t>
+  </si>
+  <si>
+    <t>236411</t>
+  </si>
+  <si>
+    <t>236500</t>
+  </si>
+  <si>
+    <t>Obaveze po osnovu dopr. za slučaj nezap. za socij.pomoć zapos.</t>
+  </si>
+  <si>
+    <t>236510</t>
+  </si>
+  <si>
+    <t>236511</t>
+  </si>
+  <si>
     <t>250000</t>
   </si>
   <si>
@@ -562,51 +613,18 @@
     <t>311112</t>
   </si>
   <si>
+    <t>311150</t>
+  </si>
+  <si>
+    <t>311151</t>
+  </si>
+  <si>
     <t>311160</t>
   </si>
   <si>
     <t>311161</t>
   </si>
   <si>
-    <t>311200</t>
-  </si>
-  <si>
-    <t>Nefinansijska imovina u zalihama</t>
-  </si>
-  <si>
-    <t>311270</t>
-  </si>
-  <si>
-    <t>311271</t>
-  </si>
-  <si>
-    <t>320000</t>
-  </si>
-  <si>
-    <t>UTVRDJIVANJE REZULTATA POSLOVANJA</t>
-  </si>
-  <si>
-    <t>321000</t>
-  </si>
-  <si>
-    <t>321100</t>
-  </si>
-  <si>
-    <t>Utvrdjivanje rezultata poslovanja</t>
-  </si>
-  <si>
-    <t>321120</t>
-  </si>
-  <si>
-    <t>Višak ili manjak prihoda i primanja</t>
-  </si>
-  <si>
-    <t>321121</t>
-  </si>
-  <si>
-    <t>Višak prihoda i primanja - suficit</t>
-  </si>
-  <si>
     <t>350000</t>
   </si>
   <si>
@@ -754,6 +772,27 @@
     <t>412211</t>
   </si>
   <si>
+    <t>414000</t>
+  </si>
+  <si>
+    <t>SOCIJALNA DAVANJA ZAPOSLENIMA</t>
+  </si>
+  <si>
+    <t>414100</t>
+  </si>
+  <si>
+    <t>Isplata naknada za vreme ods.sa posla na ter.fond.</t>
+  </si>
+  <si>
+    <t>414120</t>
+  </si>
+  <si>
+    <t>Bolovanje preko 30 dana</t>
+  </si>
+  <si>
+    <t>414121</t>
+  </si>
+  <si>
     <t>415000</t>
   </si>
   <si>
@@ -910,6 +949,18 @@
     <t>Usluge mobilnog telefona</t>
   </si>
   <si>
+    <t>421420</t>
+  </si>
+  <si>
+    <t>Usluge pošte i dostave</t>
+  </si>
+  <si>
+    <t>421421</t>
+  </si>
+  <si>
+    <t>Pošta</t>
+  </si>
+  <si>
     <t>421500</t>
   </si>
   <si>
@@ -928,12 +979,42 @@
     <t>Osiguranje zgrada</t>
   </si>
   <si>
+    <t>421520</t>
+  </si>
+  <si>
+    <t>Osiguranje zaposlenih</t>
+  </si>
+  <si>
+    <t>421521</t>
+  </si>
+  <si>
+    <t>Osiguranje zaposlenih u slučaju nesreće na radu</t>
+  </si>
+  <si>
+    <t>421522</t>
+  </si>
+  <si>
+    <t>Zdravstveno osiguranje zaposlenih</t>
+  </si>
+  <si>
     <t>421600</t>
   </si>
   <si>
     <t>ZAKUP IMOVINE I OPREME</t>
   </si>
   <si>
+    <t>421610</t>
+  </si>
+  <si>
+    <t>ZAKUP IMOVINE</t>
+  </si>
+  <si>
+    <t>421619</t>
+  </si>
+  <si>
+    <t>ZAKUP OSTALOG PROSTORA</t>
+  </si>
+  <si>
     <t>421620</t>
   </si>
   <si>
@@ -967,6 +1048,24 @@
     <t>USLUGE PO UGOVORU</t>
   </si>
   <si>
+    <t>423200</t>
+  </si>
+  <si>
+    <t>Kompjuterske usluge</t>
+  </si>
+  <si>
+    <t>423210</t>
+  </si>
+  <si>
+    <t>Usluge za izradu i održavanje softvera</t>
+  </si>
+  <si>
+    <t>423212</t>
+  </si>
+  <si>
+    <t>Usluge za održavanje softvera</t>
+  </si>
+  <si>
     <t>423700</t>
   </si>
   <si>
@@ -1024,6 +1123,27 @@
     <t>Ostale usluge i materijali za tek.popr. i održ.zgrada</t>
   </si>
   <si>
+    <t>425200</t>
+  </si>
+  <si>
+    <t>Tekuće popravke i održavanje opreme</t>
+  </si>
+  <si>
+    <t>425220</t>
+  </si>
+  <si>
+    <t>Tekuće popravke i održavanje administrativne opreme</t>
+  </si>
+  <si>
+    <t>425225</t>
+  </si>
+  <si>
+    <t>425227</t>
+  </si>
+  <si>
+    <t>Ugradna oprema</t>
+  </si>
+  <si>
     <t>426000</t>
   </si>
   <si>
@@ -1045,6 +1165,42 @@
     <t>426111</t>
   </si>
   <si>
+    <t>426300</t>
+  </si>
+  <si>
+    <t>Materijali za obrazovanje i usavršavanje zaposlenih</t>
+  </si>
+  <si>
+    <t>426310</t>
+  </si>
+  <si>
+    <t>Publikacije, časopisi i glasila</t>
+  </si>
+  <si>
+    <t>426311</t>
+  </si>
+  <si>
+    <t>Stručna literatura za redovne potrebe zaposlenih</t>
+  </si>
+  <si>
+    <t>426400</t>
+  </si>
+  <si>
+    <t>Materijali za saobraćaj</t>
+  </si>
+  <si>
+    <t>426410</t>
+  </si>
+  <si>
+    <t>Izdaci za gorivo</t>
+  </si>
+  <si>
+    <t>426412</t>
+  </si>
+  <si>
+    <t>Dizel gorivo</t>
+  </si>
+  <si>
     <t>426900</t>
   </si>
   <si>
@@ -1054,10 +1210,49 @@
     <t>426910</t>
   </si>
   <si>
-    <t>426913</t>
-  </si>
-  <si>
-    <t>Alat i inventar</t>
+    <t>426919</t>
+  </si>
+  <si>
+    <t>Ostali materijali za posebne namene</t>
+  </si>
+  <si>
+    <t>500000</t>
+  </si>
+  <si>
+    <t>IZDACI ZA NEFINANSIJSKU IMOVINU</t>
+  </si>
+  <si>
+    <t>510000</t>
+  </si>
+  <si>
+    <t>OSNOVNA SREDSTVA</t>
+  </si>
+  <si>
+    <t>512000</t>
+  </si>
+  <si>
+    <t>MAŠINE I OPREMA</t>
+  </si>
+  <si>
+    <t>512200</t>
+  </si>
+  <si>
+    <t>512210</t>
+  </si>
+  <si>
+    <t>kancelarijska oprema oprema</t>
+  </si>
+  <si>
+    <t>512212</t>
+  </si>
+  <si>
+    <t>512220</t>
+  </si>
+  <si>
+    <t>512222</t>
+  </si>
+  <si>
+    <t>Štampači</t>
   </si>
   <si>
     <t>700000</t>
@@ -1461,7 +1656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J206"/>
+  <dimension ref="A1:J244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
@@ -1471,8 +1666,7 @@
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1563,25 +1757,25 @@
         <v>11</v>
       </c>
       <c r="C5" s="6">
-        <v>11257733.95</v>
+        <v>8374883.60</v>
       </c>
       <c r="D5" s="6">
-        <v>8894751.640000001</v>
+        <v>6628787.02</v>
       </c>
       <c r="E5" s="6">
-        <v>801806.2</v>
+        <v>179556.40</v>
       </c>
       <c r="F5" s="6">
-        <v>809041</v>
+        <v>89778.20</v>
       </c>
       <c r="G5" s="6">
-        <v>12059540.15</v>
+        <v>8554440.00</v>
       </c>
       <c r="H5" s="6">
-        <v>9703792.640000001</v>
+        <v>6718565.22</v>
       </c>
       <c r="I5" s="6">
-        <v>2355747.51</v>
+        <v>1835874.78</v>
       </c>
       <c r="J5" s="6">
         <v>0</v>
@@ -1595,25 +1789,25 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>11203983.95</v>
+        <v>8374883.60</v>
       </c>
       <c r="D6" s="6">
-        <v>8894751.640000001</v>
+        <v>6628787.02</v>
       </c>
       <c r="E6" s="6">
-        <v>801806.2</v>
+        <v>179556.40</v>
       </c>
       <c r="F6" s="6">
-        <v>809041</v>
+        <v>89778.20</v>
       </c>
       <c r="G6" s="6">
-        <v>12005790.15</v>
+        <v>8554440.00</v>
       </c>
       <c r="H6" s="6">
-        <v>9703792.640000001</v>
+        <v>6718565.22</v>
       </c>
       <c r="I6" s="6">
-        <v>2301997.51</v>
+        <v>1835874.78</v>
       </c>
       <c r="J6" s="6">
         <v>0</v>
@@ -1627,25 +1821,25 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>10883076.45</v>
+        <v>8053976.10</v>
       </c>
       <c r="D7" s="6">
-        <v>8894751.640000001</v>
+        <v>6628787.02</v>
       </c>
       <c r="E7" s="6">
-        <v>801806.2</v>
+        <v>89778.20</v>
       </c>
       <c r="F7" s="6">
-        <v>809041</v>
+        <v>0.00</v>
       </c>
       <c r="G7" s="6">
-        <v>11684882.65</v>
+        <v>8143754.30</v>
       </c>
       <c r="H7" s="6">
-        <v>9703792.640000001</v>
+        <v>6628787.02</v>
       </c>
       <c r="I7" s="6">
-        <v>1981090.01</v>
+        <v>1514967.28</v>
       </c>
       <c r="J7" s="6">
         <v>0</v>
@@ -1659,25 +1853,25 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>10883076.45</v>
+        <v>8053976.10</v>
       </c>
       <c r="D8" s="6">
-        <v>8894751.640000001</v>
+        <v>6628787.02</v>
       </c>
       <c r="E8" s="6">
-        <v>801806.2</v>
+        <v>89778.20</v>
       </c>
       <c r="F8" s="6">
-        <v>809041</v>
+        <v>0.00</v>
       </c>
       <c r="G8" s="6">
-        <v>11684882.65</v>
+        <v>8143754.30</v>
       </c>
       <c r="H8" s="6">
-        <v>9703792.640000001</v>
+        <v>6628787.02</v>
       </c>
       <c r="I8" s="6">
-        <v>1981090.01</v>
+        <v>1514967.28</v>
       </c>
       <c r="J8" s="6">
         <v>0</v>
@@ -1691,25 +1885,25 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>1720521.04</v>
+        <v>8053976.10</v>
       </c>
       <c r="D9" s="6">
-        <v>1720521.04</v>
+        <v>6628787.02</v>
       </c>
       <c r="E9" s="6">
-        <v>0</v>
+        <v>89778.20</v>
       </c>
       <c r="F9" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G9" s="6">
-        <v>1720521.04</v>
+        <v>8143754.30</v>
       </c>
       <c r="H9" s="6">
-        <v>1720521.04</v>
+        <v>6628787.02</v>
       </c>
       <c r="I9" s="6">
-        <v>0</v>
+        <v>1514967.28</v>
       </c>
       <c r="J9" s="6">
         <v>0</v>
@@ -1723,25 +1917,25 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>1720521.04</v>
+        <v>2564312.67</v>
       </c>
       <c r="D10" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E10" s="6">
-        <v>0</v>
+        <v>39799.20</v>
       </c>
       <c r="F10" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G10" s="6">
-        <v>1720521.04</v>
+        <v>2604111.87</v>
       </c>
       <c r="H10" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I10" s="6">
-        <v>1720521.04</v>
+        <v>2604111.87</v>
       </c>
       <c r="J10" s="6">
         <v>0</v>
@@ -1755,28 +1949,28 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>0</v>
+        <v>3788376.97</v>
       </c>
       <c r="D11" s="6">
-        <v>1720521.04</v>
+        <v>0.00</v>
       </c>
       <c r="E11" s="6">
-        <v>0</v>
+        <v>49979.00</v>
       </c>
       <c r="F11" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G11" s="6">
-        <v>0</v>
+        <v>3838355.97</v>
       </c>
       <c r="H11" s="6">
-        <v>1720521.04</v>
+        <v>0.00</v>
       </c>
       <c r="I11" s="6">
-        <v>0</v>
+        <v>3838355.97</v>
       </c>
       <c r="J11" s="6">
-        <v>1720521.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1787,25 +1981,25 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>9162555.41</v>
+        <v>383128.28</v>
       </c>
       <c r="D12" s="6">
-        <v>7174230.6</v>
+        <v>0.00</v>
       </c>
       <c r="E12" s="6">
-        <v>801806.2</v>
+        <v>0.00</v>
       </c>
       <c r="F12" s="6">
-        <v>809041</v>
+        <v>0.00</v>
       </c>
       <c r="G12" s="6">
-        <v>9964361.609999999</v>
+        <v>383128.28</v>
       </c>
       <c r="H12" s="6">
-        <v>7983271.6</v>
+        <v>0.00</v>
       </c>
       <c r="I12" s="6">
-        <v>1981090.01</v>
+        <v>383128.28</v>
       </c>
       <c r="J12" s="6">
         <v>0</v>
@@ -1819,25 +2013,25 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>2633099.65</v>
+        <v>1289168.18</v>
       </c>
       <c r="D13" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E13" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="F13" s="6">
-        <v>60388.87</v>
+        <v>0.00</v>
       </c>
       <c r="G13" s="6">
-        <v>2633099.65</v>
+        <v>1289168.18</v>
       </c>
       <c r="H13" s="6">
-        <v>60388.87</v>
+        <v>0.00</v>
       </c>
       <c r="I13" s="6">
-        <v>2572710.78</v>
+        <v>1289168.18</v>
       </c>
       <c r="J13" s="6">
         <v>0</v>
@@ -1851,25 +2045,25 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>4674872.89</v>
+        <v>28990.00</v>
       </c>
       <c r="D14" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E14" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="F14" s="6">
-        <v>708029.9300000001</v>
+        <v>0.00</v>
       </c>
       <c r="G14" s="6">
-        <v>4674872.89</v>
+        <v>28990.00</v>
       </c>
       <c r="H14" s="6">
-        <v>708029.9300000001</v>
+        <v>0.00</v>
       </c>
       <c r="I14" s="6">
-        <v>3966842.96</v>
+        <v>28990.00</v>
       </c>
       <c r="J14" s="6">
         <v>0</v>
@@ -1883,28 +2077,28 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>451813.28</v>
+        <v>0.00</v>
       </c>
       <c r="D15" s="6">
-        <v>0</v>
+        <v>6628787.02</v>
       </c>
       <c r="E15" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="F15" s="6">
-        <v>32412</v>
+        <v>0.00</v>
       </c>
       <c r="G15" s="6">
-        <v>451813.28</v>
+        <v>0.00</v>
       </c>
       <c r="H15" s="6">
-        <v>32412</v>
+        <v>6628787.02</v>
       </c>
       <c r="I15" s="6">
-        <v>419401.28</v>
+        <v>0</v>
       </c>
       <c r="J15" s="6">
-        <v>0</v>
+        <v>6628787.02</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1915,25 +2109,25 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>1335380.79</v>
+        <v>0.00</v>
       </c>
       <c r="D16" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E16" s="6">
-        <v>0</v>
+        <v>89778.20</v>
       </c>
       <c r="F16" s="6">
-        <v>7670</v>
+        <v>89778.20</v>
       </c>
       <c r="G16" s="6">
-        <v>1335380.79</v>
+        <v>89778.20</v>
       </c>
       <c r="H16" s="6">
-        <v>7670</v>
+        <v>89778.20</v>
       </c>
       <c r="I16" s="6">
-        <v>1327710.79</v>
+        <v>0</v>
       </c>
       <c r="J16" s="6">
         <v>0</v>
@@ -1947,25 +2141,25 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>67388.8</v>
+        <v>0.00</v>
       </c>
       <c r="D17" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E17" s="6">
-        <v>0</v>
+        <v>89778.20</v>
       </c>
       <c r="F17" s="6">
-        <v>0</v>
+        <v>89778.20</v>
       </c>
       <c r="G17" s="6">
-        <v>67388.8</v>
+        <v>89778.20</v>
       </c>
       <c r="H17" s="6">
-        <v>0</v>
+        <v>89778.20</v>
       </c>
       <c r="I17" s="6">
-        <v>67388.8</v>
+        <v>0</v>
       </c>
       <c r="J17" s="6">
         <v>0</v>
@@ -1979,28 +2173,28 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D18" s="6">
-        <v>7174230.6</v>
+        <v>0.00</v>
       </c>
       <c r="E18" s="6">
-        <v>801806.2</v>
+        <v>89778.20</v>
       </c>
       <c r="F18" s="6">
-        <v>540.2</v>
+        <v>89778.20</v>
       </c>
       <c r="G18" s="6">
-        <v>801806.2</v>
+        <v>89778.20</v>
       </c>
       <c r="H18" s="6">
-        <v>7174770.8</v>
+        <v>89778.20</v>
       </c>
       <c r="I18" s="6">
         <v>0</v>
       </c>
       <c r="J18" s="6">
-        <v>6372964.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2011,25 +2205,25 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>320907.5</v>
+        <v>0.00</v>
       </c>
       <c r="D19" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E19" s="6">
-        <v>0</v>
+        <v>89778.20</v>
       </c>
       <c r="F19" s="6">
-        <v>0</v>
+        <v>89778.20</v>
       </c>
       <c r="G19" s="6">
-        <v>320907.5</v>
+        <v>89778.20</v>
       </c>
       <c r="H19" s="6">
-        <v>0</v>
+        <v>89778.20</v>
       </c>
       <c r="I19" s="6">
-        <v>320907.5</v>
+        <v>0</v>
       </c>
       <c r="J19" s="6">
         <v>0</v>
@@ -2043,25 +2237,25 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>320907.5</v>
+        <v>320907.50</v>
       </c>
       <c r="D20" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E20" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="F20" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G20" s="6">
-        <v>320907.5</v>
+        <v>320907.50</v>
       </c>
       <c r="H20" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I20" s="6">
-        <v>320907.5</v>
+        <v>320907.50</v>
       </c>
       <c r="J20" s="6">
         <v>0</v>
@@ -2075,25 +2269,25 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>320907.5</v>
+        <v>320907.50</v>
       </c>
       <c r="D21" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E21" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="F21" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G21" s="6">
-        <v>320907.5</v>
+        <v>320907.50</v>
       </c>
       <c r="H21" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I21" s="6">
-        <v>320907.5</v>
+        <v>320907.50</v>
       </c>
       <c r="J21" s="6">
         <v>0</v>
@@ -2104,28 +2298,28 @@
         <v>44</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>320907.5</v>
+        <v>320907.50</v>
       </c>
       <c r="D22" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E22" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="F22" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G22" s="6">
-        <v>320907.5</v>
+        <v>320907.50</v>
       </c>
       <c r="H22" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I22" s="6">
-        <v>320907.5</v>
+        <v>320907.50</v>
       </c>
       <c r="J22" s="6">
         <v>0</v>
@@ -2133,31 +2327,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>46</v>
-      </c>
       <c r="C23" s="6">
-        <v>53750</v>
+        <v>320907.50</v>
       </c>
       <c r="D23" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E23" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="F23" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G23" s="6">
-        <v>53750</v>
+        <v>320907.50</v>
       </c>
       <c r="H23" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I23" s="6">
-        <v>53750</v>
+        <v>320907.50</v>
       </c>
       <c r="J23" s="6">
         <v>0</v>
@@ -2171,25 +2365,25 @@
         <v>48</v>
       </c>
       <c r="C24" s="6">
-        <v>53750</v>
+        <v>4625138.02</v>
       </c>
       <c r="D24" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E24" s="6">
-        <v>0</v>
+        <v>39985690.97</v>
       </c>
       <c r="F24" s="6">
-        <v>0</v>
+        <v>42693248.27</v>
       </c>
       <c r="G24" s="6">
-        <v>53750</v>
+        <v>44610828.99</v>
       </c>
       <c r="H24" s="6">
-        <v>0</v>
+        <v>42693248.27</v>
       </c>
       <c r="I24" s="6">
-        <v>53750</v>
+        <v>1917580.72</v>
       </c>
       <c r="J24" s="6">
         <v>0</v>
@@ -2203,25 +2397,25 @@
         <v>50</v>
       </c>
       <c r="C25" s="6">
-        <v>53750</v>
+        <v>1686447.18</v>
       </c>
       <c r="D25" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E25" s="6">
-        <v>0</v>
+        <v>21592590.09</v>
       </c>
       <c r="F25" s="6">
-        <v>0</v>
+        <v>21881599.11</v>
       </c>
       <c r="G25" s="6">
-        <v>53750</v>
+        <v>23279037.27</v>
       </c>
       <c r="H25" s="6">
-        <v>0</v>
+        <v>21881599.11</v>
       </c>
       <c r="I25" s="6">
-        <v>53750</v>
+        <v>1397438.16</v>
       </c>
       <c r="J25" s="6">
         <v>0</v>
@@ -2232,28 +2426,28 @@
         <v>51</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C26" s="6">
-        <v>53750</v>
+        <v>0.00</v>
       </c>
       <c r="D26" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E26" s="6">
-        <v>0</v>
+        <v>20811649.16</v>
       </c>
       <c r="F26" s="6">
-        <v>0</v>
+        <v>20811649.16</v>
       </c>
       <c r="G26" s="6">
-        <v>53750</v>
+        <v>20811649.16</v>
       </c>
       <c r="H26" s="6">
-        <v>0</v>
+        <v>20811649.16</v>
       </c>
       <c r="I26" s="6">
-        <v>53750</v>
+        <v>0</v>
       </c>
       <c r="J26" s="6">
         <v>0</v>
@@ -2261,31 +2455,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>52</v>
-      </c>
       <c r="C27" s="6">
-        <v>53750</v>
+        <v>0.00</v>
       </c>
       <c r="D27" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E27" s="6">
-        <v>0</v>
+        <v>20811649.16</v>
       </c>
       <c r="F27" s="6">
-        <v>0</v>
+        <v>20811649.16</v>
       </c>
       <c r="G27" s="6">
-        <v>53750</v>
+        <v>20811649.16</v>
       </c>
       <c r="H27" s="6">
-        <v>0</v>
+        <v>20811649.16</v>
       </c>
       <c r="I27" s="6">
-        <v>53750</v>
+        <v>0</v>
       </c>
       <c r="J27" s="6">
         <v>0</v>
@@ -2296,28 +2490,28 @@
         <v>54</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C28" s="6">
-        <v>2890048.81</v>
+        <v>0.00</v>
       </c>
       <c r="D28" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E28" s="6">
-        <v>13073890.96</v>
+        <v>20811649.16</v>
       </c>
       <c r="F28" s="6">
-        <v>14278590.83</v>
+        <v>20811649.16</v>
       </c>
       <c r="G28" s="6">
-        <v>15963939.77</v>
+        <v>20811649.16</v>
       </c>
       <c r="H28" s="6">
-        <v>14278590.83</v>
+        <v>20811649.16</v>
       </c>
       <c r="I28" s="6">
-        <v>1685348.94</v>
+        <v>0</v>
       </c>
       <c r="J28" s="6">
         <v>0</v>
@@ -2325,31 +2519,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C29" s="6">
-        <v>784795.6</v>
+        <v>0.00</v>
       </c>
       <c r="D29" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E29" s="6">
-        <v>7042709.12</v>
+        <v>20811649.16</v>
       </c>
       <c r="F29" s="6">
-        <v>7235881.71</v>
+        <v>20811649.16</v>
       </c>
       <c r="G29" s="6">
-        <v>7827504.72</v>
+        <v>20811649.16</v>
       </c>
       <c r="H29" s="6">
-        <v>7235881.71</v>
+        <v>20811649.16</v>
       </c>
       <c r="I29" s="6">
-        <v>591623.01</v>
+        <v>0</v>
       </c>
       <c r="J29" s="6">
         <v>0</v>
@@ -2357,31 +2551,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C30" s="6">
-        <v>271.5</v>
+        <v>0.00</v>
       </c>
       <c r="D30" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E30" s="6">
-        <v>7042709.12</v>
+        <v>312014.11</v>
       </c>
       <c r="F30" s="6">
-        <v>7042709.12</v>
+        <v>312014.08</v>
       </c>
       <c r="G30" s="6">
-        <v>7042980.62</v>
+        <v>312014.11</v>
       </c>
       <c r="H30" s="6">
-        <v>7042709.12</v>
+        <v>312014.08</v>
       </c>
       <c r="I30" s="6">
-        <v>271.5</v>
+        <v>0.03</v>
       </c>
       <c r="J30" s="6">
         <v>0</v>
@@ -2395,25 +2589,25 @@
         <v>60</v>
       </c>
       <c r="C31" s="6">
-        <v>271.5</v>
+        <v>0.00</v>
       </c>
       <c r="D31" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E31" s="6">
-        <v>7042709.12</v>
+        <v>312014.11</v>
       </c>
       <c r="F31" s="6">
-        <v>7042709.12</v>
+        <v>312014.08</v>
       </c>
       <c r="G31" s="6">
-        <v>7042980.62</v>
+        <v>312014.11</v>
       </c>
       <c r="H31" s="6">
-        <v>7042709.12</v>
+        <v>312014.08</v>
       </c>
       <c r="I31" s="6">
-        <v>271.5</v>
+        <v>0.03</v>
       </c>
       <c r="J31" s="6">
         <v>0</v>
@@ -2424,28 +2618,28 @@
         <v>61</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C32" s="6">
-        <v>271.5</v>
+        <v>0.00</v>
       </c>
       <c r="D32" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E32" s="6">
-        <v>7042709.12</v>
+        <v>312014.11</v>
       </c>
       <c r="F32" s="6">
-        <v>7042709.12</v>
+        <v>312014.08</v>
       </c>
       <c r="G32" s="6">
-        <v>7042980.62</v>
+        <v>312014.11</v>
       </c>
       <c r="H32" s="6">
-        <v>7042709.12</v>
+        <v>312014.08</v>
       </c>
       <c r="I32" s="6">
-        <v>271.5</v>
+        <v>0.03</v>
       </c>
       <c r="J32" s="6">
         <v>0</v>
@@ -2453,31 +2647,31 @@
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C33" s="6">
-        <v>271.5</v>
+        <v>0.00</v>
       </c>
       <c r="D33" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E33" s="6">
-        <v>7042709.12</v>
+        <v>312014.11</v>
       </c>
       <c r="F33" s="6">
-        <v>7042709.12</v>
+        <v>312014.08</v>
       </c>
       <c r="G33" s="6">
-        <v>7042980.62</v>
+        <v>312014.11</v>
       </c>
       <c r="H33" s="6">
-        <v>7042709.12</v>
+        <v>312014.08</v>
       </c>
       <c r="I33" s="6">
-        <v>271.5</v>
+        <v>0.03</v>
       </c>
       <c r="J33" s="6">
         <v>0</v>
@@ -2485,31 +2679,31 @@
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C34" s="6">
-        <v>2542.59</v>
+        <v>1686447.18</v>
       </c>
       <c r="D34" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E34" s="6">
-        <v>0</v>
+        <v>468926.82</v>
       </c>
       <c r="F34" s="6">
-        <v>0</v>
+        <v>757935.87</v>
       </c>
       <c r="G34" s="6">
-        <v>2542.59</v>
+        <v>2155374.00</v>
       </c>
       <c r="H34" s="6">
-        <v>0</v>
+        <v>757935.87</v>
       </c>
       <c r="I34" s="6">
-        <v>2542.59</v>
+        <v>1397438.13</v>
       </c>
       <c r="J34" s="6">
         <v>0</v>
@@ -2517,31 +2711,31 @@
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C35" s="6">
-        <v>2542.59</v>
+        <v>1686447.18</v>
       </c>
       <c r="D35" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E35" s="6">
-        <v>0</v>
+        <v>468926.82</v>
       </c>
       <c r="F35" s="6">
-        <v>0</v>
+        <v>757935.87</v>
       </c>
       <c r="G35" s="6">
-        <v>2542.59</v>
+        <v>2155374.00</v>
       </c>
       <c r="H35" s="6">
-        <v>0</v>
+        <v>757935.87</v>
       </c>
       <c r="I35" s="6">
-        <v>2542.59</v>
+        <v>1397438.13</v>
       </c>
       <c r="J35" s="6">
         <v>0</v>
@@ -2549,31 +2743,31 @@
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C36" s="6">
-        <v>2542.59</v>
+        <v>86411.69</v>
       </c>
       <c r="D36" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E36" s="6">
-        <v>0</v>
+        <v>189979.00</v>
       </c>
       <c r="F36" s="6">
-        <v>0</v>
+        <v>204078.05</v>
       </c>
       <c r="G36" s="6">
-        <v>2542.59</v>
+        <v>276390.69</v>
       </c>
       <c r="H36" s="6">
-        <v>0</v>
+        <v>204078.05</v>
       </c>
       <c r="I36" s="6">
-        <v>2542.59</v>
+        <v>72312.64</v>
       </c>
       <c r="J36" s="6">
         <v>0</v>
@@ -2581,31 +2775,31 @@
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>71</v>
-      </c>
       <c r="C37" s="6">
-        <v>2542.59</v>
+        <v>86411.69</v>
       </c>
       <c r="D37" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E37" s="6">
-        <v>0</v>
+        <v>189979.00</v>
       </c>
       <c r="F37" s="6">
-        <v>0</v>
+        <v>204078.05</v>
       </c>
       <c r="G37" s="6">
-        <v>2542.59</v>
+        <v>276390.69</v>
       </c>
       <c r="H37" s="6">
-        <v>0</v>
+        <v>204078.05</v>
       </c>
       <c r="I37" s="6">
-        <v>2542.59</v>
+        <v>72312.64</v>
       </c>
       <c r="J37" s="6">
         <v>0</v>
@@ -2619,25 +2813,25 @@
         <v>73</v>
       </c>
       <c r="C38" s="6">
-        <v>781981.51</v>
+        <v>1600035.49</v>
       </c>
       <c r="D38" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E38" s="6">
-        <v>0</v>
+        <v>278947.82</v>
       </c>
       <c r="F38" s="6">
-        <v>193172.59</v>
+        <v>553857.82</v>
       </c>
       <c r="G38" s="6">
-        <v>781981.51</v>
+        <v>1878983.31</v>
       </c>
       <c r="H38" s="6">
-        <v>193172.59</v>
+        <v>553857.82</v>
       </c>
       <c r="I38" s="6">
-        <v>588808.92</v>
+        <v>1325125.49</v>
       </c>
       <c r="J38" s="6">
         <v>0</v>
@@ -2648,28 +2842,28 @@
         <v>74</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C39" s="6">
-        <v>781981.51</v>
+        <v>1600035.49</v>
       </c>
       <c r="D39" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E39" s="6">
-        <v>0</v>
+        <v>278947.82</v>
       </c>
       <c r="F39" s="6">
-        <v>193172.59</v>
+        <v>553857.82</v>
       </c>
       <c r="G39" s="6">
-        <v>781981.51</v>
+        <v>1878983.31</v>
       </c>
       <c r="H39" s="6">
-        <v>193172.59</v>
+        <v>553857.82</v>
       </c>
       <c r="I39" s="6">
-        <v>588808.92</v>
+        <v>1325125.49</v>
       </c>
       <c r="J39" s="6">
         <v>0</v>
@@ -2677,31 +2871,31 @@
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="C40" s="6">
-        <v>295223.02</v>
+        <v>2938690.84</v>
       </c>
       <c r="D40" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E40" s="6">
-        <v>0</v>
+        <v>18393100.88</v>
       </c>
       <c r="F40" s="6">
-        <v>69753.59</v>
+        <v>20811649.16</v>
       </c>
       <c r="G40" s="6">
-        <v>295223.02</v>
+        <v>21331791.72</v>
       </c>
       <c r="H40" s="6">
-        <v>69753.59</v>
+        <v>20811649.16</v>
       </c>
       <c r="I40" s="6">
-        <v>225469.43</v>
+        <v>520142.56</v>
       </c>
       <c r="J40" s="6">
         <v>0</v>
@@ -2709,31 +2903,31 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C41" s="6">
-        <v>295223.02</v>
+        <v>2938690.84</v>
       </c>
       <c r="D41" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E41" s="6">
-        <v>0</v>
+        <v>18393100.88</v>
       </c>
       <c r="F41" s="6">
-        <v>69753.59</v>
+        <v>20811649.16</v>
       </c>
       <c r="G41" s="6">
-        <v>295223.02</v>
+        <v>21331791.72</v>
       </c>
       <c r="H41" s="6">
-        <v>69753.59</v>
+        <v>20811649.16</v>
       </c>
       <c r="I41" s="6">
-        <v>225469.43</v>
+        <v>520142.56</v>
       </c>
       <c r="J41" s="6">
         <v>0</v>
@@ -2741,31 +2935,31 @@
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>80</v>
-      </c>
       <c r="C42" s="6">
-        <v>486758.49</v>
+        <v>2938690.84</v>
       </c>
       <c r="D42" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E42" s="6">
-        <v>0</v>
+        <v>18393100.88</v>
       </c>
       <c r="F42" s="6">
-        <v>123419</v>
+        <v>20811649.16</v>
       </c>
       <c r="G42" s="6">
-        <v>486758.49</v>
+        <v>21331791.72</v>
       </c>
       <c r="H42" s="6">
-        <v>123419</v>
+        <v>20811649.16</v>
       </c>
       <c r="I42" s="6">
-        <v>363339.49</v>
+        <v>520142.56</v>
       </c>
       <c r="J42" s="6">
         <v>0</v>
@@ -2773,31 +2967,31 @@
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C43" s="6">
-        <v>486758.49</v>
+        <v>2938690.84</v>
       </c>
       <c r="D43" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E43" s="6">
-        <v>0</v>
+        <v>18393100.88</v>
       </c>
       <c r="F43" s="6">
-        <v>123419</v>
+        <v>20811649.16</v>
       </c>
       <c r="G43" s="6">
-        <v>486758.49</v>
+        <v>21331791.72</v>
       </c>
       <c r="H43" s="6">
-        <v>123419</v>
+        <v>20811649.16</v>
       </c>
       <c r="I43" s="6">
-        <v>363339.49</v>
+        <v>520142.56</v>
       </c>
       <c r="J43" s="6">
         <v>0</v>
@@ -2805,31 +2999,31 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="C44" s="6">
-        <v>2105253.21</v>
+        <v>2938690.84</v>
       </c>
       <c r="D44" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E44" s="6">
-        <v>6031181.84</v>
+        <v>18393100.88</v>
       </c>
       <c r="F44" s="6">
-        <v>7042709.12</v>
+        <v>20811649.16</v>
       </c>
       <c r="G44" s="6">
-        <v>8136435.05</v>
+        <v>21331791.72</v>
       </c>
       <c r="H44" s="6">
-        <v>7042709.12</v>
+        <v>20811649.16</v>
       </c>
       <c r="I44" s="6">
-        <v>1093725.93</v>
+        <v>520142.56</v>
       </c>
       <c r="J44" s="6">
         <v>0</v>
@@ -2837,34 +3031,34 @@
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="C45" s="6">
-        <v>2105253.21</v>
+        <v>0.00</v>
       </c>
       <c r="D45" s="6">
-        <v>0</v>
+        <v>4625138.02</v>
       </c>
       <c r="E45" s="6">
-        <v>6031181.84</v>
+        <v>21881599.11</v>
       </c>
       <c r="F45" s="6">
-        <v>7042709.12</v>
+        <v>19172041.81</v>
       </c>
       <c r="G45" s="6">
-        <v>8136435.05</v>
+        <v>21881599.11</v>
       </c>
       <c r="H45" s="6">
-        <v>7042709.12</v>
+        <v>23797179.83</v>
       </c>
       <c r="I45" s="6">
-        <v>1093725.93</v>
+        <v>0</v>
       </c>
       <c r="J45" s="6">
-        <v>0</v>
+        <v>1915580.72</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2875,25 +3069,25 @@
         <v>86</v>
       </c>
       <c r="C46" s="6">
-        <v>2105253.21</v>
+        <v>0.00</v>
       </c>
       <c r="D46" s="6">
-        <v>0</v>
+        <v>2254178.21</v>
       </c>
       <c r="E46" s="6">
-        <v>6031181.84</v>
+        <v>14796547.81</v>
       </c>
       <c r="F46" s="6">
-        <v>7042709.12</v>
+        <v>12542369.60</v>
       </c>
       <c r="G46" s="6">
-        <v>8136435.05</v>
+        <v>14796547.81</v>
       </c>
       <c r="H46" s="6">
-        <v>7042709.12</v>
+        <v>14796547.81</v>
       </c>
       <c r="I46" s="6">
-        <v>1093725.93</v>
+        <v>0</v>
       </c>
       <c r="J46" s="6">
         <v>0</v>
@@ -2904,28 +3098,28 @@
         <v>87</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C47" s="6">
-        <v>2105253.21</v>
+        <v>0.00</v>
       </c>
       <c r="D47" s="6">
-        <v>0</v>
+        <v>1573769.52</v>
       </c>
       <c r="E47" s="6">
-        <v>6031181.84</v>
+        <v>11939779.14</v>
       </c>
       <c r="F47" s="6">
-        <v>7042709.12</v>
+        <v>10366009.62</v>
       </c>
       <c r="G47" s="6">
-        <v>8136435.05</v>
+        <v>11939779.14</v>
       </c>
       <c r="H47" s="6">
-        <v>7042709.12</v>
+        <v>11939779.14</v>
       </c>
       <c r="I47" s="6">
-        <v>1093725.93</v>
+        <v>0</v>
       </c>
       <c r="J47" s="6">
         <v>0</v>
@@ -2933,31 +3127,31 @@
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C48" s="6">
-        <v>2105253.21</v>
+        <v>0.00</v>
       </c>
       <c r="D48" s="6">
-        <v>0</v>
+        <v>1139932.37</v>
       </c>
       <c r="E48" s="6">
-        <v>6031181.84</v>
+        <v>8645893.81</v>
       </c>
       <c r="F48" s="6">
-        <v>7042709.12</v>
+        <v>7505961.44</v>
       </c>
       <c r="G48" s="6">
-        <v>8136435.05</v>
+        <v>8645893.81</v>
       </c>
       <c r="H48" s="6">
-        <v>7042709.12</v>
+        <v>8645893.81</v>
       </c>
       <c r="I48" s="6">
-        <v>1093725.93</v>
+        <v>0</v>
       </c>
       <c r="J48" s="6">
         <v>0</v>
@@ -2965,34 +3159,34 @@
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>91</v>
-      </c>
       <c r="C49" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D49" s="6">
-        <v>2889777.31</v>
+        <v>1139932.37</v>
       </c>
       <c r="E49" s="6">
-        <v>7405408.21</v>
+        <v>8645893.81</v>
       </c>
       <c r="F49" s="6">
-        <v>6200708.34</v>
+        <v>7505961.44</v>
       </c>
       <c r="G49" s="6">
-        <v>7405408.21</v>
+        <v>8645893.81</v>
       </c>
       <c r="H49" s="6">
-        <v>9090485.65</v>
+        <v>8645893.81</v>
       </c>
       <c r="I49" s="6">
         <v>0</v>
       </c>
       <c r="J49" s="6">
-        <v>1685077.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -3000,569 +3194,569 @@
         <v>92</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C50" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D50" s="6">
-        <v>1486326.97</v>
+        <v>1139932.37</v>
       </c>
       <c r="E50" s="6">
-        <v>5418466.39</v>
+        <v>8645893.81</v>
       </c>
       <c r="F50" s="6">
-        <v>4786120.06</v>
+        <v>7505961.44</v>
       </c>
       <c r="G50" s="6">
-        <v>5418466.39</v>
+        <v>8645893.81</v>
       </c>
       <c r="H50" s="6">
-        <v>6272447.03</v>
+        <v>8645893.81</v>
       </c>
       <c r="I50" s="6">
         <v>0</v>
       </c>
       <c r="J50" s="6">
-        <v>853980.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B51" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>95</v>
-      </c>
       <c r="C51" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D51" s="6">
-        <v>1290774.61</v>
+        <v>121379.02</v>
       </c>
       <c r="E51" s="6">
-        <v>4374742.13</v>
+        <v>922742.19</v>
       </c>
       <c r="F51" s="6">
-        <v>3825592.04</v>
+        <v>801363.17</v>
       </c>
       <c r="G51" s="6">
-        <v>4374742.13</v>
+        <v>922742.19</v>
       </c>
       <c r="H51" s="6">
-        <v>5116366.65</v>
+        <v>922742.19</v>
       </c>
       <c r="I51" s="6">
         <v>0</v>
       </c>
       <c r="J51" s="6">
-        <v>741624.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C52" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D52" s="6">
-        <v>937931.39</v>
+        <v>121379.02</v>
       </c>
       <c r="E52" s="6">
-        <v>3172129.35</v>
+        <v>922742.19</v>
       </c>
       <c r="F52" s="6">
-        <v>2771860.12</v>
+        <v>801363.17</v>
       </c>
       <c r="G52" s="6">
-        <v>3172129.35</v>
+        <v>922742.19</v>
       </c>
       <c r="H52" s="6">
-        <v>3709791.51</v>
+        <v>922742.19</v>
       </c>
       <c r="I52" s="6">
         <v>0</v>
       </c>
       <c r="J52" s="6">
-        <v>537662.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C53" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D53" s="6">
-        <v>937931.39</v>
+        <v>121379.02</v>
       </c>
       <c r="E53" s="6">
-        <v>3172129.35</v>
+        <v>922742.19</v>
       </c>
       <c r="F53" s="6">
-        <v>2771860.12</v>
+        <v>801363.17</v>
       </c>
       <c r="G53" s="6">
-        <v>3172129.35</v>
+        <v>922742.19</v>
       </c>
       <c r="H53" s="6">
-        <v>3709791.51</v>
+        <v>922742.19</v>
       </c>
       <c r="I53" s="6">
         <v>0</v>
       </c>
       <c r="J53" s="6">
-        <v>537662.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C54" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D54" s="6">
-        <v>937931.39</v>
+        <v>220327.73</v>
       </c>
       <c r="E54" s="6">
-        <v>3172129.35</v>
+        <v>1671569.12</v>
       </c>
       <c r="F54" s="6">
-        <v>2771860.12</v>
+        <v>1451241.39</v>
       </c>
       <c r="G54" s="6">
-        <v>3172129.35</v>
+        <v>1671569.12</v>
       </c>
       <c r="H54" s="6">
-        <v>3709791.51</v>
+        <v>1671569.12</v>
       </c>
       <c r="I54" s="6">
         <v>0</v>
       </c>
       <c r="J54" s="6">
-        <v>537662.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C55" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D55" s="6">
-        <v>95979.07000000001</v>
+        <v>220327.73</v>
       </c>
       <c r="E55" s="6">
-        <v>333179.04</v>
+        <v>1671569.12</v>
       </c>
       <c r="F55" s="6">
-        <v>293862.43</v>
+        <v>1451241.39</v>
       </c>
       <c r="G55" s="6">
-        <v>333179.04</v>
+        <v>1671569.12</v>
       </c>
       <c r="H55" s="6">
-        <v>389841.5</v>
+        <v>1671569.12</v>
       </c>
       <c r="I55" s="6">
         <v>0</v>
       </c>
       <c r="J55" s="6">
-        <v>56662.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C56" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D56" s="6">
-        <v>95979.07000000001</v>
+        <v>220327.73</v>
       </c>
       <c r="E56" s="6">
-        <v>333179.04</v>
+        <v>1671569.12</v>
       </c>
       <c r="F56" s="6">
-        <v>293862.43</v>
+        <v>1451241.39</v>
       </c>
       <c r="G56" s="6">
-        <v>333179.04</v>
+        <v>1671569.12</v>
       </c>
       <c r="H56" s="6">
-        <v>389841.5</v>
+        <v>1671569.12</v>
       </c>
       <c r="I56" s="6">
         <v>0</v>
       </c>
       <c r="J56" s="6">
-        <v>56662.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C57" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D57" s="6">
-        <v>95979.07000000001</v>
+        <v>81049.14</v>
       </c>
       <c r="E57" s="6">
-        <v>333179.04</v>
+        <v>614898.60</v>
       </c>
       <c r="F57" s="6">
-        <v>293862.43</v>
+        <v>533849.46</v>
       </c>
       <c r="G57" s="6">
-        <v>333179.04</v>
+        <v>614898.60</v>
       </c>
       <c r="H57" s="6">
-        <v>389841.5</v>
+        <v>614898.60</v>
       </c>
       <c r="I57" s="6">
         <v>0</v>
       </c>
       <c r="J57" s="6">
-        <v>56662.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C58" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D58" s="6">
-        <v>180708.45</v>
+        <v>81049.14</v>
       </c>
       <c r="E58" s="6">
-        <v>612463.91</v>
+        <v>614898.60</v>
       </c>
       <c r="F58" s="6">
-        <v>535582.9</v>
+        <v>533849.46</v>
       </c>
       <c r="G58" s="6">
-        <v>612463.91</v>
+        <v>614898.60</v>
       </c>
       <c r="H58" s="6">
-        <v>716291.35</v>
+        <v>614898.60</v>
       </c>
       <c r="I58" s="6">
         <v>0</v>
       </c>
       <c r="J58" s="6">
-        <v>103827.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C59" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D59" s="6">
-        <v>180708.45</v>
+        <v>81049.14</v>
       </c>
       <c r="E59" s="6">
-        <v>612463.91</v>
+        <v>614898.60</v>
       </c>
       <c r="F59" s="6">
-        <v>535582.9</v>
+        <v>533849.46</v>
       </c>
       <c r="G59" s="6">
-        <v>612463.91</v>
+        <v>614898.60</v>
       </c>
       <c r="H59" s="6">
-        <v>716291.35</v>
+        <v>614898.60</v>
       </c>
       <c r="I59" s="6">
         <v>0</v>
       </c>
       <c r="J59" s="6">
-        <v>103827.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C60" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D60" s="6">
-        <v>180708.45</v>
+        <v>11081.26</v>
       </c>
       <c r="E60" s="6">
-        <v>612463.91</v>
+        <v>84675.42</v>
       </c>
       <c r="F60" s="6">
-        <v>535582.9</v>
+        <v>73594.16</v>
       </c>
       <c r="G60" s="6">
-        <v>612463.91</v>
+        <v>84675.42</v>
       </c>
       <c r="H60" s="6">
-        <v>716291.35</v>
+        <v>84675.42</v>
       </c>
       <c r="I60" s="6">
         <v>0</v>
       </c>
       <c r="J60" s="6">
-        <v>103827.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C61" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D61" s="6">
-        <v>66474.89</v>
+        <v>11081.26</v>
       </c>
       <c r="E61" s="6">
-        <v>225299.23</v>
+        <v>84675.42</v>
       </c>
       <c r="F61" s="6">
-        <v>197018</v>
+        <v>73594.16</v>
       </c>
       <c r="G61" s="6">
-        <v>225299.23</v>
+        <v>84675.42</v>
       </c>
       <c r="H61" s="6">
-        <v>263492.89</v>
+        <v>84675.42</v>
       </c>
       <c r="I61" s="6">
         <v>0</v>
       </c>
       <c r="J61" s="6">
-        <v>38193.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C62" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D62" s="6">
-        <v>66474.89</v>
+        <v>11081.26</v>
       </c>
       <c r="E62" s="6">
-        <v>225299.23</v>
+        <v>84675.42</v>
       </c>
       <c r="F62" s="6">
-        <v>197018</v>
+        <v>73594.16</v>
       </c>
       <c r="G62" s="6">
-        <v>225299.23</v>
+        <v>84675.42</v>
       </c>
       <c r="H62" s="6">
-        <v>263492.89</v>
+        <v>84675.42</v>
       </c>
       <c r="I62" s="6">
         <v>0</v>
       </c>
       <c r="J62" s="6">
-        <v>38193.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C63" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D63" s="6">
-        <v>66474.89</v>
+        <v>59796.49</v>
       </c>
       <c r="E63" s="6">
-        <v>225299.23</v>
+        <v>420672.90</v>
       </c>
       <c r="F63" s="6">
-        <v>197018</v>
+        <v>360876.41</v>
       </c>
       <c r="G63" s="6">
-        <v>225299.23</v>
+        <v>420672.90</v>
       </c>
       <c r="H63" s="6">
-        <v>263492.89</v>
+        <v>420672.90</v>
       </c>
       <c r="I63" s="6">
         <v>0</v>
       </c>
       <c r="J63" s="6">
-        <v>38193.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B64" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B64" s="5" t="s">
-        <v>113</v>
-      </c>
       <c r="C64" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D64" s="6">
-        <v>9680.809999999999</v>
+        <v>57489.04</v>
       </c>
       <c r="E64" s="6">
-        <v>31670.6</v>
+        <v>405214.47</v>
       </c>
       <c r="F64" s="6">
-        <v>27268.59</v>
+        <v>347725.43</v>
       </c>
       <c r="G64" s="6">
-        <v>31670.6</v>
+        <v>405214.47</v>
       </c>
       <c r="H64" s="6">
-        <v>36949.4</v>
+        <v>405214.47</v>
       </c>
       <c r="I64" s="6">
         <v>0</v>
       </c>
       <c r="J64" s="6">
-        <v>5278.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C65" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D65" s="6">
-        <v>9680.809999999999</v>
+        <v>57489.04</v>
       </c>
       <c r="E65" s="6">
-        <v>31670.6</v>
+        <v>405214.47</v>
       </c>
       <c r="F65" s="6">
-        <v>27268.59</v>
+        <v>347725.43</v>
       </c>
       <c r="G65" s="6">
-        <v>31670.6</v>
+        <v>405214.47</v>
       </c>
       <c r="H65" s="6">
-        <v>36949.4</v>
+        <v>405214.47</v>
       </c>
       <c r="I65" s="6">
         <v>0</v>
       </c>
       <c r="J65" s="6">
-        <v>5278.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C66" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D66" s="6">
-        <v>9680.809999999999</v>
+        <v>57489.04</v>
       </c>
       <c r="E66" s="6">
-        <v>31670.6</v>
+        <v>405214.47</v>
       </c>
       <c r="F66" s="6">
-        <v>27268.59</v>
+        <v>347725.43</v>
       </c>
       <c r="G66" s="6">
-        <v>31670.6</v>
+        <v>405214.47</v>
       </c>
       <c r="H66" s="6">
-        <v>36949.4</v>
+        <v>405214.47</v>
       </c>
       <c r="I66" s="6">
         <v>0</v>
       </c>
       <c r="J66" s="6">
-        <v>5278.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B67" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B67" s="5" t="s">
-        <v>117</v>
-      </c>
       <c r="C67" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D67" s="6">
-        <v>0</v>
+        <v>2307.45</v>
       </c>
       <c r="E67" s="6">
-        <v>195587.01</v>
+        <v>15458.43</v>
       </c>
       <c r="F67" s="6">
-        <v>195587.01</v>
+        <v>13150.98</v>
       </c>
       <c r="G67" s="6">
-        <v>195587.01</v>
+        <v>15458.43</v>
       </c>
       <c r="H67" s="6">
-        <v>195587.01</v>
+        <v>15458.43</v>
       </c>
       <c r="I67" s="6">
         <v>0</v>
@@ -3573,28 +3767,28 @@
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C68" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D68" s="6">
-        <v>0</v>
+        <v>2307.45</v>
       </c>
       <c r="E68" s="6">
-        <v>188871</v>
+        <v>15458.43</v>
       </c>
       <c r="F68" s="6">
-        <v>188871</v>
+        <v>13150.98</v>
       </c>
       <c r="G68" s="6">
-        <v>188871</v>
+        <v>15458.43</v>
       </c>
       <c r="H68" s="6">
-        <v>188871</v>
+        <v>15458.43</v>
       </c>
       <c r="I68" s="6">
         <v>0</v>
@@ -3605,28 +3799,28 @@
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>119</v>
       </c>
       <c r="C69" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D69" s="6">
-        <v>0</v>
+        <v>2307.45</v>
       </c>
       <c r="E69" s="6">
-        <v>188871</v>
+        <v>15458.43</v>
       </c>
       <c r="F69" s="6">
-        <v>188871</v>
+        <v>13150.98</v>
       </c>
       <c r="G69" s="6">
-        <v>188871</v>
+        <v>15458.43</v>
       </c>
       <c r="H69" s="6">
-        <v>188871</v>
+        <v>15458.43</v>
       </c>
       <c r="I69" s="6">
         <v>0</v>
@@ -3637,28 +3831,28 @@
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B70" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B70" s="5" t="s">
-        <v>119</v>
-      </c>
       <c r="C70" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D70" s="6">
-        <v>0</v>
+        <v>315205.10</v>
       </c>
       <c r="E70" s="6">
-        <v>188871</v>
+        <v>315205.10</v>
       </c>
       <c r="F70" s="6">
-        <v>188871</v>
+        <v>0.00</v>
       </c>
       <c r="G70" s="6">
-        <v>188871</v>
+        <v>315205.10</v>
       </c>
       <c r="H70" s="6">
-        <v>188871</v>
+        <v>315205.10</v>
       </c>
       <c r="I70" s="6">
         <v>0</v>
@@ -3675,22 +3869,22 @@
         <v>123</v>
       </c>
       <c r="C71" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D71" s="6">
-        <v>0</v>
+        <v>286499.79</v>
       </c>
       <c r="E71" s="6">
-        <v>6716.01</v>
+        <v>286499.79</v>
       </c>
       <c r="F71" s="6">
-        <v>6716.01</v>
+        <v>0.00</v>
       </c>
       <c r="G71" s="6">
-        <v>6716.01</v>
+        <v>286499.79</v>
       </c>
       <c r="H71" s="6">
-        <v>6716.01</v>
+        <v>286499.79</v>
       </c>
       <c r="I71" s="6">
         <v>0</v>
@@ -3707,22 +3901,22 @@
         <v>123</v>
       </c>
       <c r="C72" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D72" s="6">
-        <v>0</v>
+        <v>286499.79</v>
       </c>
       <c r="E72" s="6">
-        <v>6716.01</v>
+        <v>286499.79</v>
       </c>
       <c r="F72" s="6">
-        <v>6716.01</v>
+        <v>0.00</v>
       </c>
       <c r="G72" s="6">
-        <v>6716.01</v>
+        <v>286499.79</v>
       </c>
       <c r="H72" s="6">
-        <v>6716.01</v>
+        <v>286499.79</v>
       </c>
       <c r="I72" s="6">
         <v>0</v>
@@ -3739,22 +3933,22 @@
         <v>126</v>
       </c>
       <c r="C73" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D73" s="6">
-        <v>0</v>
+        <v>286499.79</v>
       </c>
       <c r="E73" s="6">
-        <v>6716.01</v>
+        <v>286499.79</v>
       </c>
       <c r="F73" s="6">
-        <v>6716.01</v>
+        <v>0.00</v>
       </c>
       <c r="G73" s="6">
-        <v>6716.01</v>
+        <v>286499.79</v>
       </c>
       <c r="H73" s="6">
-        <v>6716.01</v>
+        <v>286499.79</v>
       </c>
       <c r="I73" s="6">
         <v>0</v>
@@ -3771,22 +3965,22 @@
         <v>128</v>
       </c>
       <c r="C74" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D74" s="6">
-        <v>0</v>
+        <v>28705.31</v>
       </c>
       <c r="E74" s="6">
-        <v>185363.78</v>
+        <v>28705.31</v>
       </c>
       <c r="F74" s="6">
-        <v>185363.78</v>
+        <v>0.00</v>
       </c>
       <c r="G74" s="6">
-        <v>185363.78</v>
+        <v>28705.31</v>
       </c>
       <c r="H74" s="6">
-        <v>185363.78</v>
+        <v>28705.31</v>
       </c>
       <c r="I74" s="6">
         <v>0</v>
@@ -3800,25 +3994,25 @@
         <v>129</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C75" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D75" s="6">
-        <v>0</v>
+        <v>28705.31</v>
       </c>
       <c r="E75" s="6">
-        <v>169526.5</v>
+        <v>28705.31</v>
       </c>
       <c r="F75" s="6">
-        <v>169526.5</v>
+        <v>0.00</v>
       </c>
       <c r="G75" s="6">
-        <v>169526.5</v>
+        <v>28705.31</v>
       </c>
       <c r="H75" s="6">
-        <v>169526.5</v>
+        <v>28705.31</v>
       </c>
       <c r="I75" s="6">
         <v>0</v>
@@ -3829,28 +4023,28 @@
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C76" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D76" s="6">
-        <v>0</v>
+        <v>28705.31</v>
       </c>
       <c r="E76" s="6">
-        <v>169526.5</v>
+        <v>28705.31</v>
       </c>
       <c r="F76" s="6">
-        <v>169526.5</v>
+        <v>0.00</v>
       </c>
       <c r="G76" s="6">
-        <v>169526.5</v>
+        <v>28705.31</v>
       </c>
       <c r="H76" s="6">
-        <v>169526.5</v>
+        <v>28705.31</v>
       </c>
       <c r="I76" s="6">
         <v>0</v>
@@ -3861,28 +4055,28 @@
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B77" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B77" s="5" t="s">
-        <v>133</v>
-      </c>
       <c r="C77" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D77" s="6">
-        <v>0</v>
+        <v>238426.11</v>
       </c>
       <c r="E77" s="6">
-        <v>169526.5</v>
+        <v>1808876.59</v>
       </c>
       <c r="F77" s="6">
-        <v>169526.5</v>
+        <v>1570450.48</v>
       </c>
       <c r="G77" s="6">
-        <v>169526.5</v>
+        <v>1808876.59</v>
       </c>
       <c r="H77" s="6">
-        <v>169526.5</v>
+        <v>1808876.59</v>
       </c>
       <c r="I77" s="6">
         <v>0</v>
@@ -3893,28 +4087,28 @@
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B78" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B78" s="5" t="s">
-        <v>135</v>
-      </c>
       <c r="C78" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D78" s="6">
-        <v>0</v>
+        <v>157376.97</v>
       </c>
       <c r="E78" s="6">
-        <v>15837.28</v>
+        <v>1193977.99</v>
       </c>
       <c r="F78" s="6">
-        <v>15837.28</v>
+        <v>1036601.02</v>
       </c>
       <c r="G78" s="6">
-        <v>15837.28</v>
+        <v>1193977.99</v>
       </c>
       <c r="H78" s="6">
-        <v>15837.28</v>
+        <v>1193977.99</v>
       </c>
       <c r="I78" s="6">
         <v>0</v>
@@ -3925,28 +4119,28 @@
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C79" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D79" s="6">
-        <v>0</v>
+        <v>157376.97</v>
       </c>
       <c r="E79" s="6">
-        <v>15837.28</v>
+        <v>1193977.99</v>
       </c>
       <c r="F79" s="6">
-        <v>15837.28</v>
+        <v>1036601.02</v>
       </c>
       <c r="G79" s="6">
-        <v>15837.28</v>
+        <v>1193977.99</v>
       </c>
       <c r="H79" s="6">
-        <v>15837.28</v>
+        <v>1193977.99</v>
       </c>
       <c r="I79" s="6">
         <v>0</v>
@@ -3957,28 +4151,28 @@
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C80" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D80" s="6">
-        <v>0</v>
+        <v>157376.97</v>
       </c>
       <c r="E80" s="6">
-        <v>15837.28</v>
+        <v>1193977.99</v>
       </c>
       <c r="F80" s="6">
-        <v>15837.28</v>
+        <v>1036601.02</v>
       </c>
       <c r="G80" s="6">
-        <v>15837.28</v>
+        <v>1193977.99</v>
       </c>
       <c r="H80" s="6">
-        <v>15837.28</v>
+        <v>1193977.99</v>
       </c>
       <c r="I80" s="6">
         <v>0</v>
@@ -3989,194 +4183,194 @@
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B81" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B81" s="5" t="s">
-        <v>139</v>
-      </c>
       <c r="C81" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D81" s="6">
-        <v>195552.36</v>
+        <v>81049.14</v>
       </c>
       <c r="E81" s="6">
-        <v>662773.47</v>
+        <v>614898.60</v>
       </c>
       <c r="F81" s="6">
-        <v>579577.23</v>
+        <v>533849.46</v>
       </c>
       <c r="G81" s="6">
-        <v>662773.47</v>
+        <v>614898.60</v>
       </c>
       <c r="H81" s="6">
-        <v>775129.59</v>
+        <v>614898.60</v>
       </c>
       <c r="I81" s="6">
         <v>0</v>
       </c>
       <c r="J81" s="6">
-        <v>112356.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C82" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D82" s="6">
-        <v>129077.47</v>
+        <v>81049.14</v>
       </c>
       <c r="E82" s="6">
-        <v>437474.24</v>
+        <v>614898.60</v>
       </c>
       <c r="F82" s="6">
-        <v>382559.23</v>
+        <v>533849.46</v>
       </c>
       <c r="G82" s="6">
-        <v>437474.24</v>
+        <v>614898.60</v>
       </c>
       <c r="H82" s="6">
-        <v>511636.7</v>
+        <v>614898.60</v>
       </c>
       <c r="I82" s="6">
         <v>0</v>
       </c>
       <c r="J82" s="6">
-        <v>74162.46000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C83" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D83" s="6">
-        <v>129077.47</v>
+        <v>81049.14</v>
       </c>
       <c r="E83" s="6">
-        <v>437474.24</v>
+        <v>614898.60</v>
       </c>
       <c r="F83" s="6">
-        <v>382559.23</v>
+        <v>533849.46</v>
       </c>
       <c r="G83" s="6">
-        <v>437474.24</v>
+        <v>614898.60</v>
       </c>
       <c r="H83" s="6">
-        <v>511636.7</v>
+        <v>614898.60</v>
       </c>
       <c r="I83" s="6">
         <v>0</v>
       </c>
       <c r="J83" s="6">
-        <v>74162.46000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C84" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D84" s="6">
-        <v>129077.47</v>
+        <v>66980.99</v>
       </c>
       <c r="E84" s="6">
-        <v>437474.24</v>
+        <v>312014.08</v>
       </c>
       <c r="F84" s="6">
-        <v>382559.23</v>
+        <v>245033.09</v>
       </c>
       <c r="G84" s="6">
-        <v>437474.24</v>
+        <v>312014.08</v>
       </c>
       <c r="H84" s="6">
-        <v>511636.7</v>
+        <v>312014.08</v>
       </c>
       <c r="I84" s="6">
         <v>0</v>
       </c>
       <c r="J84" s="6">
-        <v>74162.46000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B85" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B85" s="5" t="s">
-        <v>145</v>
-      </c>
       <c r="C85" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D85" s="6">
-        <v>66474.89</v>
+        <v>43360.00</v>
       </c>
       <c r="E85" s="6">
-        <v>225299.23</v>
+        <v>201055.97</v>
       </c>
       <c r="F85" s="6">
-        <v>197018</v>
+        <v>157695.97</v>
       </c>
       <c r="G85" s="6">
-        <v>225299.23</v>
+        <v>201055.97</v>
       </c>
       <c r="H85" s="6">
-        <v>263492.89</v>
+        <v>201055.97</v>
       </c>
       <c r="I85" s="6">
         <v>0</v>
       </c>
       <c r="J85" s="6">
-        <v>38193.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B86" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B86" s="5" t="s">
-        <v>145</v>
-      </c>
       <c r="C86" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D86" s="6">
-        <v>66474.89</v>
+        <v>43360.00</v>
       </c>
       <c r="E86" s="6">
-        <v>225299.23</v>
+        <v>201055.97</v>
       </c>
       <c r="F86" s="6">
-        <v>197018</v>
+        <v>157695.97</v>
       </c>
       <c r="G86" s="6">
-        <v>225299.23</v>
+        <v>201055.97</v>
       </c>
       <c r="H86" s="6">
-        <v>263492.89</v>
+        <v>201055.97</v>
       </c>
       <c r="I86" s="6">
         <v>0</v>
       </c>
       <c r="J86" s="6">
-        <v>38193.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:10">
@@ -4184,95 +4378,95 @@
         <v>147</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C87" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D87" s="6">
-        <v>66474.89</v>
+        <v>43360.00</v>
       </c>
       <c r="E87" s="6">
-        <v>225299.23</v>
+        <v>201055.97</v>
       </c>
       <c r="F87" s="6">
-        <v>197018</v>
+        <v>157695.97</v>
       </c>
       <c r="G87" s="6">
-        <v>225299.23</v>
+        <v>201055.97</v>
       </c>
       <c r="H87" s="6">
-        <v>263492.89</v>
+        <v>201055.97</v>
       </c>
       <c r="I87" s="6">
         <v>0</v>
       </c>
       <c r="J87" s="6">
-        <v>38193.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C88" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D88" s="6">
-        <v>618926.24</v>
+        <v>3232.94</v>
       </c>
       <c r="E88" s="6">
-        <v>1793769.23</v>
+        <v>15985.51</v>
       </c>
       <c r="F88" s="6">
-        <v>1414588.28</v>
+        <v>12752.57</v>
       </c>
       <c r="G88" s="6">
-        <v>1793769.23</v>
+        <v>15985.51</v>
       </c>
       <c r="H88" s="6">
-        <v>2033514.52</v>
+        <v>15985.51</v>
       </c>
       <c r="I88" s="6">
         <v>0</v>
       </c>
       <c r="J88" s="6">
-        <v>239745.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B89" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B89" s="5" t="s">
-        <v>151</v>
-      </c>
       <c r="C89" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D89" s="6">
-        <v>618926.24</v>
+        <v>3232.94</v>
       </c>
       <c r="E89" s="6">
-        <v>1793769.23</v>
+        <v>15985.51</v>
       </c>
       <c r="F89" s="6">
-        <v>1414588.28</v>
+        <v>12752.57</v>
       </c>
       <c r="G89" s="6">
-        <v>1793769.23</v>
+        <v>15985.51</v>
       </c>
       <c r="H89" s="6">
-        <v>2033514.52</v>
+        <v>15985.51</v>
       </c>
       <c r="I89" s="6">
         <v>0</v>
       </c>
       <c r="J89" s="6">
-        <v>239745.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:10">
@@ -4280,63 +4474,63 @@
         <v>152</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C90" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D90" s="6">
-        <v>618926.24</v>
+        <v>3232.94</v>
       </c>
       <c r="E90" s="6">
-        <v>1793769.23</v>
+        <v>15985.51</v>
       </c>
       <c r="F90" s="6">
-        <v>1414588.28</v>
+        <v>12752.57</v>
       </c>
       <c r="G90" s="6">
-        <v>1793769.23</v>
+        <v>15985.51</v>
       </c>
       <c r="H90" s="6">
-        <v>2033514.52</v>
+        <v>15985.51</v>
       </c>
       <c r="I90" s="6">
         <v>0</v>
       </c>
       <c r="J90" s="6">
-        <v>239745.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B91" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B91" s="5" t="s">
-        <v>153</v>
-      </c>
       <c r="C91" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D91" s="6">
-        <v>618926.24</v>
+        <v>13960.43</v>
       </c>
       <c r="E91" s="6">
-        <v>1793769.23</v>
+        <v>65031.16</v>
       </c>
       <c r="F91" s="6">
-        <v>1414588.28</v>
+        <v>51070.73</v>
       </c>
       <c r="G91" s="6">
-        <v>1793769.23</v>
+        <v>65031.16</v>
       </c>
       <c r="H91" s="6">
-        <v>2033514.52</v>
+        <v>65031.16</v>
       </c>
       <c r="I91" s="6">
         <v>0</v>
       </c>
       <c r="J91" s="6">
-        <v>239745.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -4344,31 +4538,31 @@
         <v>155</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C92" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D92" s="6">
-        <v>618926.24</v>
+        <v>13960.43</v>
       </c>
       <c r="E92" s="6">
-        <v>1793769.23</v>
+        <v>65031.16</v>
       </c>
       <c r="F92" s="6">
-        <v>1414588.28</v>
+        <v>51070.73</v>
       </c>
       <c r="G92" s="6">
-        <v>1793769.23</v>
+        <v>65031.16</v>
       </c>
       <c r="H92" s="6">
-        <v>2033514.52</v>
+        <v>65031.16</v>
       </c>
       <c r="I92" s="6">
         <v>0</v>
       </c>
       <c r="J92" s="6">
-        <v>239745.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -4376,63 +4570,63 @@
         <v>156</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C93" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D93" s="6">
-        <v>784524.1</v>
+        <v>13960.43</v>
       </c>
       <c r="E93" s="6">
-        <v>193172.59</v>
+        <v>65031.16</v>
       </c>
       <c r="F93" s="6">
-        <v>0</v>
+        <v>51070.73</v>
       </c>
       <c r="G93" s="6">
-        <v>193172.59</v>
+        <v>65031.16</v>
       </c>
       <c r="H93" s="6">
-        <v>784524.1</v>
+        <v>65031.16</v>
       </c>
       <c r="I93" s="6">
         <v>0</v>
       </c>
       <c r="J93" s="6">
-        <v>591351.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B94" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B94" s="5" t="s">
-        <v>157</v>
-      </c>
       <c r="C94" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D94" s="6">
-        <v>784524.1</v>
+        <v>5991.36</v>
       </c>
       <c r="E94" s="6">
-        <v>193172.59</v>
+        <v>27909.22</v>
       </c>
       <c r="F94" s="6">
-        <v>0</v>
+        <v>21917.86</v>
       </c>
       <c r="G94" s="6">
-        <v>193172.59</v>
+        <v>27909.22</v>
       </c>
       <c r="H94" s="6">
-        <v>784524.1</v>
+        <v>27909.22</v>
       </c>
       <c r="I94" s="6">
         <v>0</v>
       </c>
       <c r="J94" s="6">
-        <v>591351.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -4440,639 +4634,639 @@
         <v>159</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C95" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D95" s="6">
-        <v>781981.51</v>
+        <v>5991.36</v>
       </c>
       <c r="E95" s="6">
-        <v>193172.59</v>
+        <v>27909.22</v>
       </c>
       <c r="F95" s="6">
-        <v>0</v>
+        <v>21917.86</v>
       </c>
       <c r="G95" s="6">
-        <v>193172.59</v>
+        <v>27909.22</v>
       </c>
       <c r="H95" s="6">
-        <v>781981.51</v>
+        <v>27909.22</v>
       </c>
       <c r="I95" s="6">
         <v>0</v>
       </c>
       <c r="J95" s="6">
-        <v>588808.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C96" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D96" s="6">
-        <v>781981.51</v>
+        <v>5991.36</v>
       </c>
       <c r="E96" s="6">
-        <v>193172.59</v>
+        <v>27909.22</v>
       </c>
       <c r="F96" s="6">
-        <v>0</v>
+        <v>21917.86</v>
       </c>
       <c r="G96" s="6">
-        <v>193172.59</v>
+        <v>27909.22</v>
       </c>
       <c r="H96" s="6">
-        <v>781981.51</v>
+        <v>27909.22</v>
       </c>
       <c r="I96" s="6">
         <v>0</v>
       </c>
       <c r="J96" s="6">
-        <v>588808.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C97" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D97" s="6">
-        <v>295223.02</v>
+        <v>436.26</v>
       </c>
       <c r="E97" s="6">
-        <v>69753.59</v>
+        <v>2032.22</v>
       </c>
       <c r="F97" s="6">
-        <v>0</v>
+        <v>1595.96</v>
       </c>
       <c r="G97" s="6">
-        <v>69753.59</v>
+        <v>2032.22</v>
       </c>
       <c r="H97" s="6">
-        <v>295223.02</v>
+        <v>2032.22</v>
       </c>
       <c r="I97" s="6">
         <v>0</v>
       </c>
       <c r="J97" s="6">
-        <v>225469.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C98" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D98" s="6">
-        <v>486758.49</v>
+        <v>436.26</v>
       </c>
       <c r="E98" s="6">
-        <v>123419</v>
+        <v>2032.22</v>
       </c>
       <c r="F98" s="6">
-        <v>0</v>
+        <v>1595.96</v>
       </c>
       <c r="G98" s="6">
-        <v>123419</v>
+        <v>2032.22</v>
       </c>
       <c r="H98" s="6">
-        <v>486758.49</v>
+        <v>2032.22</v>
       </c>
       <c r="I98" s="6">
         <v>0</v>
       </c>
       <c r="J98" s="6">
-        <v>363339.49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C99" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D99" s="6">
-        <v>2542.59</v>
+        <v>436.26</v>
       </c>
       <c r="E99" s="6">
-        <v>0</v>
+        <v>2032.22</v>
       </c>
       <c r="F99" s="6">
-        <v>0</v>
+        <v>1595.96</v>
       </c>
       <c r="G99" s="6">
-        <v>0</v>
+        <v>2032.22</v>
       </c>
       <c r="H99" s="6">
-        <v>2542.59</v>
+        <v>2032.22</v>
       </c>
       <c r="I99" s="6">
         <v>0</v>
       </c>
       <c r="J99" s="6">
-        <v>2542.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:10">
       <c r="A100" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C100" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D100" s="6">
-        <v>2542.59</v>
+        <v>684512.63</v>
       </c>
       <c r="E100" s="6">
-        <v>0</v>
+        <v>6015101.35</v>
       </c>
       <c r="F100" s="6">
-        <v>0</v>
+        <v>5848731.28</v>
       </c>
       <c r="G100" s="6">
-        <v>0</v>
+        <v>6015101.35</v>
       </c>
       <c r="H100" s="6">
-        <v>2542.59</v>
+        <v>6533243.91</v>
       </c>
       <c r="I100" s="6">
         <v>0</v>
       </c>
       <c r="J100" s="6">
-        <v>2542.59</v>
+        <v>518142.56</v>
       </c>
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C101" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D101" s="6">
-        <v>2542.59</v>
+        <v>684512.63</v>
       </c>
       <c r="E101" s="6">
-        <v>0</v>
+        <v>6015101.35</v>
       </c>
       <c r="F101" s="6">
-        <v>0</v>
+        <v>5848731.28</v>
       </c>
       <c r="G101" s="6">
-        <v>0</v>
+        <v>6015101.35</v>
       </c>
       <c r="H101" s="6">
-        <v>2542.59</v>
+        <v>6533243.91</v>
       </c>
       <c r="I101" s="6">
         <v>0</v>
       </c>
       <c r="J101" s="6">
-        <v>2542.59</v>
+        <v>518142.56</v>
       </c>
     </row>
     <row r="102" spans="1:10">
       <c r="A102" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C102" s="6">
-        <v>231700.02</v>
+        <v>0.00</v>
       </c>
       <c r="D102" s="6">
-        <v>2594953.83</v>
+        <v>684512.63</v>
       </c>
       <c r="E102" s="6">
-        <v>15184.8</v>
+        <v>6015101.35</v>
       </c>
       <c r="F102" s="6">
-        <v>7950</v>
+        <v>5848731.28</v>
       </c>
       <c r="G102" s="6">
-        <v>246884.82</v>
+        <v>6015101.35</v>
       </c>
       <c r="H102" s="6">
-        <v>2602903.83</v>
+        <v>6533243.91</v>
       </c>
       <c r="I102" s="6">
         <v>0</v>
       </c>
       <c r="J102" s="6">
-        <v>2356019.01</v>
+        <v>518142.56</v>
       </c>
     </row>
     <row r="103" spans="1:10">
       <c r="A103" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C103" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D103" s="6">
-        <v>2362982.31</v>
+        <v>684512.63</v>
       </c>
       <c r="E103" s="6">
-        <v>7234.8</v>
+        <v>6015101.35</v>
       </c>
       <c r="F103" s="6">
-        <v>0</v>
+        <v>5848731.28</v>
       </c>
       <c r="G103" s="6">
-        <v>7234.8</v>
+        <v>6015101.35</v>
       </c>
       <c r="H103" s="6">
-        <v>2362982.31</v>
+        <v>6533243.91</v>
       </c>
       <c r="I103" s="6">
         <v>0</v>
       </c>
       <c r="J103" s="6">
-        <v>2355747.51</v>
+        <v>518142.56</v>
       </c>
     </row>
     <row r="104" spans="1:10">
       <c r="A104" s="4" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C104" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D104" s="6">
-        <v>2362982.31</v>
+        <v>684512.63</v>
       </c>
       <c r="E104" s="6">
-        <v>7234.8</v>
+        <v>6015101.35</v>
       </c>
       <c r="F104" s="6">
-        <v>0</v>
+        <v>5848731.28</v>
       </c>
       <c r="G104" s="6">
-        <v>7234.8</v>
+        <v>6015101.35</v>
       </c>
       <c r="H104" s="6">
-        <v>2362982.31</v>
+        <v>6533243.91</v>
       </c>
       <c r="I104" s="6">
         <v>0</v>
       </c>
       <c r="J104" s="6">
-        <v>2355747.51</v>
+        <v>518142.56</v>
       </c>
     </row>
     <row r="105" spans="1:10">
       <c r="A105" s="4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C105" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D105" s="6">
-        <v>2309232.31</v>
+        <v>1686447.18</v>
       </c>
       <c r="E105" s="6">
-        <v>7234.8</v>
+        <v>1069949.95</v>
       </c>
       <c r="F105" s="6">
-        <v>0</v>
+        <v>780940.93</v>
       </c>
       <c r="G105" s="6">
-        <v>7234.8</v>
+        <v>1069949.95</v>
       </c>
       <c r="H105" s="6">
-        <v>2309232.31</v>
+        <v>2467388.11</v>
       </c>
       <c r="I105" s="6">
         <v>0</v>
       </c>
       <c r="J105" s="6">
-        <v>2301997.51</v>
+        <v>1397438.16</v>
       </c>
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C106" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D106" s="6">
-        <v>1988324.81</v>
+        <v>1686447.18</v>
       </c>
       <c r="E106" s="6">
-        <v>7234.8</v>
+        <v>1069949.95</v>
       </c>
       <c r="F106" s="6">
-        <v>0</v>
+        <v>780940.93</v>
       </c>
       <c r="G106" s="6">
-        <v>7234.8</v>
+        <v>1069949.95</v>
       </c>
       <c r="H106" s="6">
-        <v>1988324.81</v>
+        <v>2467388.11</v>
       </c>
       <c r="I106" s="6">
         <v>0</v>
       </c>
       <c r="J106" s="6">
-        <v>1981090.01</v>
+        <v>1397438.16</v>
       </c>
     </row>
     <row r="107" spans="1:10">
       <c r="A107" s="4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>17</v>
+        <v>177</v>
       </c>
       <c r="C107" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D107" s="6">
-        <v>1988324.81</v>
+        <v>1686447.18</v>
       </c>
       <c r="E107" s="6">
-        <v>7234.8</v>
+        <v>757935.87</v>
       </c>
       <c r="F107" s="6">
-        <v>0</v>
+        <v>468926.82</v>
       </c>
       <c r="G107" s="6">
-        <v>7234.8</v>
+        <v>757935.87</v>
       </c>
       <c r="H107" s="6">
-        <v>1988324.81</v>
+        <v>2155374.00</v>
       </c>
       <c r="I107" s="6">
         <v>0</v>
       </c>
       <c r="J107" s="6">
-        <v>1981090.01</v>
+        <v>1397438.13</v>
       </c>
     </row>
     <row r="108" spans="1:10">
       <c r="A108" s="4" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>41</v>
+        <v>179</v>
       </c>
       <c r="C108" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D108" s="6">
-        <v>320907.5</v>
+        <v>1686447.18</v>
       </c>
       <c r="E108" s="6">
-        <v>0</v>
+        <v>757935.87</v>
       </c>
       <c r="F108" s="6">
-        <v>0</v>
+        <v>468926.82</v>
       </c>
       <c r="G108" s="6">
-        <v>0</v>
+        <v>757935.87</v>
       </c>
       <c r="H108" s="6">
-        <v>320907.5</v>
+        <v>2155374.00</v>
       </c>
       <c r="I108" s="6">
         <v>0</v>
       </c>
       <c r="J108" s="6">
-        <v>320907.5</v>
+        <v>1397438.13</v>
       </c>
     </row>
     <row r="109" spans="1:10">
       <c r="A109" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>41</v>
+        <v>181</v>
       </c>
       <c r="C109" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D109" s="6">
-        <v>320907.5</v>
+        <v>86411.69</v>
       </c>
       <c r="E109" s="6">
-        <v>0</v>
+        <v>194078.05</v>
       </c>
       <c r="F109" s="6">
-        <v>0</v>
+        <v>189979.00</v>
       </c>
       <c r="G109" s="6">
-        <v>0</v>
+        <v>194078.05</v>
       </c>
       <c r="H109" s="6">
-        <v>320907.5</v>
+        <v>276390.69</v>
       </c>
       <c r="I109" s="6">
         <v>0</v>
       </c>
       <c r="J109" s="6">
-        <v>320907.5</v>
+        <v>82312.64</v>
       </c>
     </row>
     <row r="110" spans="1:10">
       <c r="A110" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C110" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D110" s="6">
-        <v>53750</v>
+        <v>1600035.49</v>
       </c>
       <c r="E110" s="6">
-        <v>0</v>
+        <v>563857.82</v>
       </c>
       <c r="F110" s="6">
-        <v>0</v>
+        <v>278947.82</v>
       </c>
       <c r="G110" s="6">
-        <v>0</v>
+        <v>563857.82</v>
       </c>
       <c r="H110" s="6">
-        <v>53750</v>
+        <v>1878983.31</v>
       </c>
       <c r="I110" s="6">
         <v>0</v>
       </c>
       <c r="J110" s="6">
-        <v>53750</v>
+        <v>1315125.49</v>
       </c>
     </row>
     <row r="111" spans="1:10">
       <c r="A111" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>50</v>
+        <v>185</v>
       </c>
       <c r="C111" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D111" s="6">
-        <v>53750</v>
+        <v>0.00</v>
       </c>
       <c r="E111" s="6">
-        <v>0</v>
+        <v>312014.08</v>
       </c>
       <c r="F111" s="6">
-        <v>0</v>
+        <v>312014.11</v>
       </c>
       <c r="G111" s="6">
-        <v>0</v>
+        <v>312014.08</v>
       </c>
       <c r="H111" s="6">
-        <v>53750</v>
+        <v>312014.11</v>
       </c>
       <c r="I111" s="6">
         <v>0</v>
       </c>
       <c r="J111" s="6">
-        <v>53750</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="112" spans="1:10">
       <c r="A112" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>50</v>
+        <v>185</v>
       </c>
       <c r="C112" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D112" s="6">
-        <v>53750</v>
+        <v>0.00</v>
       </c>
       <c r="E112" s="6">
-        <v>0</v>
+        <v>312014.08</v>
       </c>
       <c r="F112" s="6">
-        <v>0</v>
+        <v>312014.11</v>
       </c>
       <c r="G112" s="6">
-        <v>0</v>
+        <v>312014.08</v>
       </c>
       <c r="H112" s="6">
-        <v>53750</v>
+        <v>312014.11</v>
       </c>
       <c r="I112" s="6">
         <v>0</v>
       </c>
       <c r="J112" s="6">
-        <v>53750</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="113" spans="1:10">
       <c r="A113" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B113" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="B113" s="5" t="s">
-        <v>189</v>
-      </c>
       <c r="C113" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D113" s="6">
-        <v>271.5</v>
+        <v>0.00</v>
       </c>
       <c r="E113" s="6">
-        <v>0</v>
+        <v>312014.08</v>
       </c>
       <c r="F113" s="6">
-        <v>0</v>
+        <v>312014.11</v>
       </c>
       <c r="G113" s="6">
-        <v>0</v>
+        <v>312014.08</v>
       </c>
       <c r="H113" s="6">
-        <v>271.5</v>
+        <v>312014.11</v>
       </c>
       <c r="I113" s="6">
         <v>0</v>
       </c>
       <c r="J113" s="6">
-        <v>271.5</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="114" spans="1:10">
       <c r="A114" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B114" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="B114" s="5" t="s">
-        <v>189</v>
-      </c>
       <c r="C114" s="6">
-        <v>0</v>
+        <v>244538.88</v>
       </c>
       <c r="D114" s="6">
-        <v>271.5</v>
+        <v>1990635.46</v>
       </c>
       <c r="E114" s="6">
-        <v>0</v>
+        <v>116767.08</v>
       </c>
       <c r="F114" s="6">
-        <v>0</v>
+        <v>206545.28</v>
       </c>
       <c r="G114" s="6">
-        <v>0</v>
+        <v>361305.96</v>
       </c>
       <c r="H114" s="6">
-        <v>271.5</v>
+        <v>2197180.74</v>
       </c>
       <c r="I114" s="6">
         <v>0</v>
       </c>
       <c r="J114" s="6">
-        <v>271.5</v>
+        <v>1835874.78</v>
       </c>
     </row>
     <row r="115" spans="1:10">
@@ -5083,28 +5277,28 @@
         <v>192</v>
       </c>
       <c r="C115" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D115" s="6">
-        <v>271.5</v>
+        <v>1746096.58</v>
       </c>
       <c r="E115" s="6">
-        <v>0</v>
+        <v>89778.20</v>
       </c>
       <c r="F115" s="6">
-        <v>0</v>
+        <v>179556.40</v>
       </c>
       <c r="G115" s="6">
-        <v>0</v>
+        <v>89778.20</v>
       </c>
       <c r="H115" s="6">
-        <v>271.5</v>
+        <v>1925652.98</v>
       </c>
       <c r="I115" s="6">
         <v>0</v>
       </c>
       <c r="J115" s="6">
-        <v>271.5</v>
+        <v>1835874.78</v>
       </c>
     </row>
     <row r="116" spans="1:10">
@@ -5112,156 +5306,156 @@
         <v>193</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C116" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D116" s="6">
-        <v>271.5</v>
+        <v>1746096.58</v>
       </c>
       <c r="E116" s="6">
-        <v>0</v>
+        <v>89778.20</v>
       </c>
       <c r="F116" s="6">
-        <v>0</v>
+        <v>179556.40</v>
       </c>
       <c r="G116" s="6">
-        <v>0</v>
+        <v>89778.20</v>
       </c>
       <c r="H116" s="6">
-        <v>271.5</v>
+        <v>1925652.98</v>
       </c>
       <c r="I116" s="6">
         <v>0</v>
       </c>
       <c r="J116" s="6">
-        <v>271.5</v>
+        <v>1835874.78</v>
       </c>
     </row>
     <row r="117" spans="1:10">
       <c r="A117" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B117" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B117" s="5" t="s">
-        <v>196</v>
-      </c>
       <c r="C117" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D117" s="6">
-        <v>271.5</v>
+        <v>1746096.58</v>
       </c>
       <c r="E117" s="6">
-        <v>0</v>
+        <v>89778.20</v>
       </c>
       <c r="F117" s="6">
-        <v>0</v>
+        <v>179556.40</v>
       </c>
       <c r="G117" s="6">
-        <v>0</v>
+        <v>89778.20</v>
       </c>
       <c r="H117" s="6">
-        <v>271.5</v>
+        <v>1925652.98</v>
       </c>
       <c r="I117" s="6">
         <v>0</v>
       </c>
       <c r="J117" s="6">
-        <v>271.5</v>
+        <v>1835874.78</v>
       </c>
     </row>
     <row r="118" spans="1:10">
       <c r="A118" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B118" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B118" s="5" t="s">
-        <v>198</v>
-      </c>
       <c r="C118" s="6">
-        <v>231700.02</v>
+        <v>0.00</v>
       </c>
       <c r="D118" s="6">
-        <v>231700.02</v>
+        <v>1425189.08</v>
       </c>
       <c r="E118" s="6">
-        <v>7950</v>
+        <v>0.00</v>
       </c>
       <c r="F118" s="6">
-        <v>7950</v>
+        <v>89778.20</v>
       </c>
       <c r="G118" s="6">
-        <v>239650.02</v>
+        <v>0.00</v>
       </c>
       <c r="H118" s="6">
-        <v>239650.02</v>
+        <v>1514967.28</v>
       </c>
       <c r="I118" s="6">
         <v>0</v>
       </c>
       <c r="J118" s="6">
-        <v>0</v>
+        <v>1514967.28</v>
       </c>
     </row>
     <row r="119" spans="1:10">
       <c r="A119" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="C119" s="6">
-        <v>231700.02</v>
+        <v>0.00</v>
       </c>
       <c r="D119" s="6">
-        <v>0</v>
+        <v>1425189.08</v>
       </c>
       <c r="E119" s="6">
-        <v>7950</v>
+        <v>0.00</v>
       </c>
       <c r="F119" s="6">
-        <v>0</v>
+        <v>89778.20</v>
       </c>
       <c r="G119" s="6">
-        <v>239650.02</v>
+        <v>0.00</v>
       </c>
       <c r="H119" s="6">
-        <v>0</v>
+        <v>1514967.28</v>
       </c>
       <c r="I119" s="6">
-        <v>239650.02</v>
+        <v>0</v>
       </c>
       <c r="J119" s="6">
-        <v>0</v>
+        <v>1514967.28</v>
       </c>
     </row>
     <row r="120" spans="1:10">
       <c r="A120" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="C120" s="6">
-        <v>231700.02</v>
+        <v>0.00</v>
       </c>
       <c r="D120" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E120" s="6">
-        <v>7950</v>
+        <v>89778.20</v>
       </c>
       <c r="F120" s="6">
-        <v>0</v>
+        <v>89778.20</v>
       </c>
       <c r="G120" s="6">
-        <v>239650.02</v>
+        <v>89778.20</v>
       </c>
       <c r="H120" s="6">
-        <v>0</v>
+        <v>89778.20</v>
       </c>
       <c r="I120" s="6">
-        <v>239650.02</v>
+        <v>0</v>
       </c>
       <c r="J120" s="6">
         <v>0</v>
@@ -5269,31 +5463,31 @@
     </row>
     <row r="121" spans="1:10">
       <c r="A121" s="4" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>204</v>
+        <v>35</v>
       </c>
       <c r="C121" s="6">
-        <v>231700.02</v>
+        <v>0.00</v>
       </c>
       <c r="D121" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E121" s="6">
-        <v>7950</v>
+        <v>89778.20</v>
       </c>
       <c r="F121" s="6">
-        <v>0</v>
+        <v>89778.20</v>
       </c>
       <c r="G121" s="6">
-        <v>239650.02</v>
+        <v>89778.20</v>
       </c>
       <c r="H121" s="6">
-        <v>0</v>
+        <v>89778.20</v>
       </c>
       <c r="I121" s="6">
-        <v>239650.02</v>
+        <v>0</v>
       </c>
       <c r="J121" s="6">
         <v>0</v>
@@ -5301,191 +5495,191 @@
     </row>
     <row r="122" spans="1:10">
       <c r="A122" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>204</v>
+        <v>43</v>
       </c>
       <c r="C122" s="6">
-        <v>231700.02</v>
+        <v>0.00</v>
       </c>
       <c r="D122" s="6">
-        <v>0</v>
+        <v>320907.50</v>
       </c>
       <c r="E122" s="6">
-        <v>7950</v>
+        <v>0.00</v>
       </c>
       <c r="F122" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G122" s="6">
-        <v>239650.02</v>
+        <v>0.00</v>
       </c>
       <c r="H122" s="6">
-        <v>0</v>
+        <v>320907.50</v>
       </c>
       <c r="I122" s="6">
-        <v>239650.02</v>
+        <v>0</v>
       </c>
       <c r="J122" s="6">
-        <v>0</v>
+        <v>320907.50</v>
       </c>
     </row>
     <row r="123" spans="1:10">
       <c r="A123" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>207</v>
+        <v>43</v>
       </c>
       <c r="C123" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D123" s="6">
-        <v>231700.02</v>
+        <v>320907.50</v>
       </c>
       <c r="E123" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="F123" s="6">
-        <v>7950</v>
+        <v>0.00</v>
       </c>
       <c r="G123" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="H123" s="6">
-        <v>239650.02</v>
+        <v>320907.50</v>
       </c>
       <c r="I123" s="6">
         <v>0</v>
       </c>
       <c r="J123" s="6">
-        <v>239650.02</v>
+        <v>320907.50</v>
       </c>
     </row>
     <row r="124" spans="1:10">
       <c r="A124" s="4" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C124" s="6">
-        <v>0</v>
+        <v>244538.88</v>
       </c>
       <c r="D124" s="6">
-        <v>231700.02</v>
+        <v>244538.88</v>
       </c>
       <c r="E124" s="6">
-        <v>0</v>
+        <v>26988.88</v>
       </c>
       <c r="F124" s="6">
-        <v>7950</v>
+        <v>26988.88</v>
       </c>
       <c r="G124" s="6">
-        <v>0</v>
+        <v>271527.76</v>
       </c>
       <c r="H124" s="6">
-        <v>239650.02</v>
+        <v>271527.76</v>
       </c>
       <c r="I124" s="6">
         <v>0</v>
       </c>
       <c r="J124" s="6">
-        <v>239650.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:10">
       <c r="A125" s="4" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C125" s="6">
-        <v>0</v>
+        <v>244538.88</v>
       </c>
       <c r="D125" s="6">
-        <v>231700.02</v>
+        <v>0.00</v>
       </c>
       <c r="E125" s="6">
-        <v>0</v>
+        <v>7950.00</v>
       </c>
       <c r="F125" s="6">
-        <v>7950</v>
+        <v>19038.88</v>
       </c>
       <c r="G125" s="6">
-        <v>0</v>
+        <v>252488.88</v>
       </c>
       <c r="H125" s="6">
-        <v>239650.02</v>
+        <v>19038.88</v>
       </c>
       <c r="I125" s="6">
-        <v>0</v>
+        <v>233450.00</v>
       </c>
       <c r="J125" s="6">
-        <v>239650.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:10">
       <c r="A126" s="4" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C126" s="6">
-        <v>0</v>
+        <v>244538.88</v>
       </c>
       <c r="D126" s="6">
-        <v>231700.02</v>
+        <v>0.00</v>
       </c>
       <c r="E126" s="6">
-        <v>0</v>
+        <v>7950.00</v>
       </c>
       <c r="F126" s="6">
-        <v>7950</v>
+        <v>19038.88</v>
       </c>
       <c r="G126" s="6">
-        <v>0</v>
+        <v>252488.88</v>
       </c>
       <c r="H126" s="6">
-        <v>239650.02</v>
+        <v>19038.88</v>
       </c>
       <c r="I126" s="6">
-        <v>0</v>
+        <v>233450.00</v>
       </c>
       <c r="J126" s="6">
-        <v>239650.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:10">
       <c r="A127" s="4" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C127" s="6">
-        <v>0</v>
+        <v>244538.88</v>
       </c>
       <c r="D127" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E127" s="6">
-        <v>7042709.12</v>
+        <v>7950.00</v>
       </c>
       <c r="F127" s="6">
-        <v>0</v>
+        <v>19038.88</v>
       </c>
       <c r="G127" s="6">
-        <v>7042709.12</v>
+        <v>252488.88</v>
       </c>
       <c r="H127" s="6">
-        <v>0</v>
+        <v>19038.88</v>
       </c>
       <c r="I127" s="6">
-        <v>7042709.12</v>
+        <v>233450.00</v>
       </c>
       <c r="J127" s="6">
         <v>0</v>
@@ -5493,31 +5687,31 @@
     </row>
     <row r="128" spans="1:10">
       <c r="A128" s="4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C128" s="6">
-        <v>0</v>
+        <v>244538.88</v>
       </c>
       <c r="D128" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E128" s="6">
-        <v>5418466.39</v>
+        <v>7950.00</v>
       </c>
       <c r="F128" s="6">
-        <v>0</v>
+        <v>19038.88</v>
       </c>
       <c r="G128" s="6">
-        <v>5418466.39</v>
+        <v>252488.88</v>
       </c>
       <c r="H128" s="6">
-        <v>0</v>
+        <v>19038.88</v>
       </c>
       <c r="I128" s="6">
-        <v>5418466.39</v>
+        <v>233450.00</v>
       </c>
       <c r="J128" s="6">
         <v>0</v>
@@ -5525,159 +5719,159 @@
     </row>
     <row r="129" spans="1:10">
       <c r="A129" s="4" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C129" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D129" s="6">
-        <v>0</v>
+        <v>244538.88</v>
       </c>
       <c r="E129" s="6">
-        <v>4374742.13</v>
+        <v>19038.88</v>
       </c>
       <c r="F129" s="6">
-        <v>0</v>
+        <v>7950.00</v>
       </c>
       <c r="G129" s="6">
-        <v>4374742.13</v>
+        <v>19038.88</v>
       </c>
       <c r="H129" s="6">
-        <v>0</v>
+        <v>252488.88</v>
       </c>
       <c r="I129" s="6">
-        <v>4374742.13</v>
+        <v>0</v>
       </c>
       <c r="J129" s="6">
-        <v>0</v>
+        <v>233450.00</v>
       </c>
     </row>
     <row r="130" spans="1:10">
       <c r="A130" s="4" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C130" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D130" s="6">
-        <v>0</v>
+        <v>244538.88</v>
       </c>
       <c r="E130" s="6">
-        <v>4374742.13</v>
+        <v>19038.88</v>
       </c>
       <c r="F130" s="6">
-        <v>0</v>
+        <v>7950.00</v>
       </c>
       <c r="G130" s="6">
-        <v>4374742.13</v>
+        <v>19038.88</v>
       </c>
       <c r="H130" s="6">
-        <v>0</v>
+        <v>252488.88</v>
       </c>
       <c r="I130" s="6">
-        <v>4374742.13</v>
+        <v>0</v>
       </c>
       <c r="J130" s="6">
-        <v>0</v>
+        <v>233450.00</v>
       </c>
     </row>
     <row r="131" spans="1:10">
       <c r="A131" s="4" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C131" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D131" s="6">
-        <v>0</v>
+        <v>244538.88</v>
       </c>
       <c r="E131" s="6">
-        <v>4374742.13</v>
+        <v>19038.88</v>
       </c>
       <c r="F131" s="6">
-        <v>0</v>
+        <v>7950.00</v>
       </c>
       <c r="G131" s="6">
-        <v>4374742.13</v>
+        <v>19038.88</v>
       </c>
       <c r="H131" s="6">
-        <v>0</v>
+        <v>252488.88</v>
       </c>
       <c r="I131" s="6">
-        <v>4374742.13</v>
+        <v>0</v>
       </c>
       <c r="J131" s="6">
-        <v>0</v>
+        <v>233450.00</v>
       </c>
     </row>
     <row r="132" spans="1:10">
       <c r="A132" s="4" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C132" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D132" s="6">
-        <v>0</v>
+        <v>244538.88</v>
       </c>
       <c r="E132" s="6">
-        <v>3353559.16</v>
+        <v>19038.88</v>
       </c>
       <c r="F132" s="6">
-        <v>0</v>
+        <v>7950.00</v>
       </c>
       <c r="G132" s="6">
-        <v>3353559.16</v>
+        <v>19038.88</v>
       </c>
       <c r="H132" s="6">
-        <v>0</v>
+        <v>252488.88</v>
       </c>
       <c r="I132" s="6">
-        <v>3353559.16</v>
+        <v>0</v>
       </c>
       <c r="J132" s="6">
-        <v>0</v>
+        <v>233450.00</v>
       </c>
     </row>
     <row r="133" spans="1:10">
       <c r="A133" s="4" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C133" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D133" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E133" s="6">
-        <v>85980.82000000001</v>
+        <v>20409856.85</v>
       </c>
       <c r="F133" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G133" s="6">
-        <v>85980.82000000001</v>
+        <v>20409856.85</v>
       </c>
       <c r="H133" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I133" s="6">
-        <v>85980.82000000001</v>
+        <v>20409856.85</v>
       </c>
       <c r="J133" s="6">
         <v>0</v>
@@ -5685,31 +5879,31 @@
     </row>
     <row r="134" spans="1:10">
       <c r="A134" s="4" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C134" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D134" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E134" s="6">
-        <v>285937.21</v>
+        <v>14484533.70</v>
       </c>
       <c r="F134" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G134" s="6">
-        <v>285937.21</v>
+        <v>14484533.70</v>
       </c>
       <c r="H134" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I134" s="6">
-        <v>285937.21</v>
+        <v>14484533.70</v>
       </c>
       <c r="J134" s="6">
         <v>0</v>
@@ -5717,31 +5911,31 @@
     </row>
     <row r="135" spans="1:10">
       <c r="A135" s="4" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C135" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D135" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E135" s="6">
-        <v>83503.44</v>
+        <v>11939779.14</v>
       </c>
       <c r="F135" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G135" s="6">
-        <v>83503.44</v>
+        <v>11939779.14</v>
       </c>
       <c r="H135" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I135" s="6">
-        <v>83503.44</v>
+        <v>11939779.14</v>
       </c>
       <c r="J135" s="6">
         <v>0</v>
@@ -5749,31 +5943,31 @@
     </row>
     <row r="136" spans="1:10">
       <c r="A136" s="4" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C136" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D136" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E136" s="6">
-        <v>511058.63</v>
+        <v>11939779.14</v>
       </c>
       <c r="F136" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G136" s="6">
-        <v>511058.63</v>
+        <v>11939779.14</v>
       </c>
       <c r="H136" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I136" s="6">
-        <v>511058.63</v>
+        <v>11939779.14</v>
       </c>
       <c r="J136" s="6">
         <v>0</v>
@@ -5781,31 +5975,31 @@
     </row>
     <row r="137" spans="1:10">
       <c r="A137" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C137" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D137" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E137" s="6">
-        <v>54702.87</v>
+        <v>11939779.14</v>
       </c>
       <c r="F137" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G137" s="6">
-        <v>54702.87</v>
+        <v>11939779.14</v>
       </c>
       <c r="H137" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I137" s="6">
-        <v>54702.87</v>
+        <v>11939779.14</v>
       </c>
       <c r="J137" s="6">
         <v>0</v>
@@ -5813,31 +6007,31 @@
     </row>
     <row r="138" spans="1:10">
       <c r="A138" s="4" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C138" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D138" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E138" s="6">
-        <v>662773.47</v>
+        <v>8197577.83</v>
       </c>
       <c r="F138" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G138" s="6">
-        <v>662773.47</v>
+        <v>8197577.83</v>
       </c>
       <c r="H138" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I138" s="6">
-        <v>662773.47</v>
+        <v>8197577.83</v>
       </c>
       <c r="J138" s="6">
         <v>0</v>
@@ -5845,31 +6039,31 @@
     </row>
     <row r="139" spans="1:10">
       <c r="A139" s="4" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C139" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D139" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E139" s="6">
-        <v>437474.24</v>
+        <v>828653.41</v>
       </c>
       <c r="F139" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G139" s="6">
-        <v>437474.24</v>
+        <v>828653.41</v>
       </c>
       <c r="H139" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I139" s="6">
-        <v>437474.24</v>
+        <v>828653.41</v>
       </c>
       <c r="J139" s="6">
         <v>0</v>
@@ -5877,31 +6071,31 @@
     </row>
     <row r="140" spans="1:10">
       <c r="A140" s="4" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C140" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D140" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E140" s="6">
-        <v>437474.24</v>
+        <v>677357.36</v>
       </c>
       <c r="F140" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G140" s="6">
-        <v>437474.24</v>
+        <v>677357.36</v>
       </c>
       <c r="H140" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I140" s="6">
-        <v>437474.24</v>
+        <v>677357.36</v>
       </c>
       <c r="J140" s="6">
         <v>0</v>
@@ -5909,31 +6103,31 @@
     </row>
     <row r="141" spans="1:10">
       <c r="A141" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C141" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D141" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E141" s="6">
-        <v>437474.24</v>
+        <v>24604.85</v>
       </c>
       <c r="F141" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G141" s="6">
-        <v>437474.24</v>
+        <v>24604.85</v>
       </c>
       <c r="H141" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I141" s="6">
-        <v>437474.24</v>
+        <v>24604.85</v>
       </c>
       <c r="J141" s="6">
         <v>0</v>
@@ -5941,31 +6135,31 @@
     </row>
     <row r="142" spans="1:10">
       <c r="A142" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C142" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D142" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E142" s="6">
-        <v>225299.23</v>
+        <v>1653789.88</v>
       </c>
       <c r="F142" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G142" s="6">
-        <v>225299.23</v>
+        <v>1653789.88</v>
       </c>
       <c r="H142" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I142" s="6">
-        <v>225299.23</v>
+        <v>1653789.88</v>
       </c>
       <c r="J142" s="6">
         <v>0</v>
@@ -5973,31 +6167,31 @@
     </row>
     <row r="143" spans="1:10">
       <c r="A143" s="4" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C143" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D143" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E143" s="6">
-        <v>225299.23</v>
+        <v>557795.81</v>
       </c>
       <c r="F143" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G143" s="6">
-        <v>225299.23</v>
+        <v>557795.81</v>
       </c>
       <c r="H143" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I143" s="6">
-        <v>225299.23</v>
+        <v>557795.81</v>
       </c>
       <c r="J143" s="6">
         <v>0</v>
@@ -6005,31 +6199,31 @@
     </row>
     <row r="144" spans="1:10">
       <c r="A144" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>242</v>
       </c>
       <c r="C144" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D144" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E144" s="6">
-        <v>225299.23</v>
+        <v>1808876.59</v>
       </c>
       <c r="F144" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G144" s="6">
-        <v>225299.23</v>
+        <v>1808876.59</v>
       </c>
       <c r="H144" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I144" s="6">
-        <v>225299.23</v>
+        <v>1808876.59</v>
       </c>
       <c r="J144" s="6">
         <v>0</v>
@@ -6037,31 +6231,31 @@
     </row>
     <row r="145" spans="1:10">
       <c r="A145" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C145" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D145" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E145" s="6">
-        <v>195587.01</v>
+        <v>1193977.99</v>
       </c>
       <c r="F145" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G145" s="6">
-        <v>195587.01</v>
+        <v>1193977.99</v>
       </c>
       <c r="H145" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I145" s="6">
-        <v>195587.01</v>
+        <v>1193977.99</v>
       </c>
       <c r="J145" s="6">
         <v>0</v>
@@ -6069,31 +6263,31 @@
     </row>
     <row r="146" spans="1:10">
       <c r="A146" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C146" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D146" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E146" s="6">
-        <v>195587.01</v>
+        <v>1193977.99</v>
       </c>
       <c r="F146" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G146" s="6">
-        <v>195587.01</v>
+        <v>1193977.99</v>
       </c>
       <c r="H146" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I146" s="6">
-        <v>195587.01</v>
+        <v>1193977.99</v>
       </c>
       <c r="J146" s="6">
         <v>0</v>
@@ -6101,31 +6295,31 @@
     </row>
     <row r="147" spans="1:10">
       <c r="A147" s="4" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C147" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D147" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E147" s="6">
-        <v>195587.01</v>
+        <v>1193977.99</v>
       </c>
       <c r="F147" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G147" s="6">
-        <v>195587.01</v>
+        <v>1193977.99</v>
       </c>
       <c r="H147" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I147" s="6">
-        <v>195587.01</v>
+        <v>1193977.99</v>
       </c>
       <c r="J147" s="6">
         <v>0</v>
@@ -6133,31 +6327,31 @@
     </row>
     <row r="148" spans="1:10">
       <c r="A148" s="4" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C148" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D148" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E148" s="6">
-        <v>195587.01</v>
+        <v>614898.60</v>
       </c>
       <c r="F148" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G148" s="6">
-        <v>195587.01</v>
+        <v>614898.60</v>
       </c>
       <c r="H148" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I148" s="6">
-        <v>195587.01</v>
+        <v>614898.60</v>
       </c>
       <c r="J148" s="6">
         <v>0</v>
@@ -6165,31 +6359,31 @@
     </row>
     <row r="149" spans="1:10">
       <c r="A149" s="4" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C149" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D149" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E149" s="6">
-        <v>185363.78</v>
+        <v>614898.60</v>
       </c>
       <c r="F149" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G149" s="6">
-        <v>185363.78</v>
+        <v>614898.60</v>
       </c>
       <c r="H149" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I149" s="6">
-        <v>185363.78</v>
+        <v>614898.60</v>
       </c>
       <c r="J149" s="6">
         <v>0</v>
@@ -6197,31 +6391,31 @@
     </row>
     <row r="150" spans="1:10">
       <c r="A150" s="4" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C150" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D150" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E150" s="6">
-        <v>185363.78</v>
+        <v>614898.60</v>
       </c>
       <c r="F150" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G150" s="6">
-        <v>185363.78</v>
+        <v>614898.60</v>
       </c>
       <c r="H150" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I150" s="6">
-        <v>185363.78</v>
+        <v>614898.60</v>
       </c>
       <c r="J150" s="6">
         <v>0</v>
@@ -6229,159 +6423,159 @@
     </row>
     <row r="151" spans="1:10">
       <c r="A151" s="4" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C151" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D151" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E151" s="6">
-        <v>185363.78</v>
+        <v>-0.03</v>
       </c>
       <c r="F151" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G151" s="6">
-        <v>185363.78</v>
+        <v>-0.03</v>
       </c>
       <c r="H151" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I151" s="6">
-        <v>185363.78</v>
+        <v>0</v>
       </c>
       <c r="J151" s="6">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="152" spans="1:10">
       <c r="A152" s="4" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C152" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D152" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E152" s="6">
-        <v>185363.78</v>
+        <v>-0.03</v>
       </c>
       <c r="F152" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G152" s="6">
-        <v>185363.78</v>
+        <v>-0.03</v>
       </c>
       <c r="H152" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I152" s="6">
-        <v>185363.78</v>
+        <v>0</v>
       </c>
       <c r="J152" s="6">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="153" spans="1:10">
       <c r="A153" s="4" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C153" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D153" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E153" s="6">
-        <v>1624242.73</v>
+        <v>-0.03</v>
       </c>
       <c r="F153" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G153" s="6">
-        <v>1624242.73</v>
+        <v>-0.03</v>
       </c>
       <c r="H153" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I153" s="6">
-        <v>1624242.73</v>
+        <v>0</v>
       </c>
       <c r="J153" s="6">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="154" spans="1:10">
       <c r="A154" s="4" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C154" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D154" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E154" s="6">
-        <v>1355534.23</v>
+        <v>-0.03</v>
       </c>
       <c r="F154" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G154" s="6">
-        <v>1355534.23</v>
+        <v>-0.03</v>
       </c>
       <c r="H154" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I154" s="6">
-        <v>1355534.23</v>
+        <v>0</v>
       </c>
       <c r="J154" s="6">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="155" spans="1:10">
       <c r="A155" s="4" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C155" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D155" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E155" s="6">
-        <v>295428.55</v>
+        <v>420672.90</v>
       </c>
       <c r="F155" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G155" s="6">
-        <v>295428.55</v>
+        <v>420672.90</v>
       </c>
       <c r="H155" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I155" s="6">
-        <v>295428.55</v>
+        <v>420672.90</v>
       </c>
       <c r="J155" s="6">
         <v>0</v>
@@ -6389,31 +6583,31 @@
     </row>
     <row r="156" spans="1:10">
       <c r="A156" s="4" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C156" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D156" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E156" s="6">
-        <v>62267.9</v>
+        <v>420672.90</v>
       </c>
       <c r="F156" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G156" s="6">
-        <v>62267.9</v>
+        <v>420672.90</v>
       </c>
       <c r="H156" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I156" s="6">
-        <v>62267.9</v>
+        <v>420672.90</v>
       </c>
       <c r="J156" s="6">
         <v>0</v>
@@ -6421,31 +6615,31 @@
     </row>
     <row r="157" spans="1:10">
       <c r="A157" s="4" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C157" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D157" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E157" s="6">
-        <v>62267.9</v>
+        <v>420672.90</v>
       </c>
       <c r="F157" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G157" s="6">
-        <v>62267.9</v>
+        <v>420672.90</v>
       </c>
       <c r="H157" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I157" s="6">
-        <v>62267.9</v>
+        <v>420672.90</v>
       </c>
       <c r="J157" s="6">
         <v>0</v>
@@ -6453,31 +6647,31 @@
     </row>
     <row r="158" spans="1:10">
       <c r="A158" s="4" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C158" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D158" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E158" s="6">
-        <v>233160.65</v>
+        <v>420672.90</v>
       </c>
       <c r="F158" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G158" s="6">
-        <v>233160.65</v>
+        <v>420672.90</v>
       </c>
       <c r="H158" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I158" s="6">
-        <v>233160.65</v>
+        <v>420672.90</v>
       </c>
       <c r="J158" s="6">
         <v>0</v>
@@ -6485,31 +6679,31 @@
     </row>
     <row r="159" spans="1:10">
       <c r="A159" s="4" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C159" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D159" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E159" s="6">
-        <v>233160.65</v>
+        <v>315205.10</v>
       </c>
       <c r="F159" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G159" s="6">
-        <v>233160.65</v>
+        <v>315205.10</v>
       </c>
       <c r="H159" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I159" s="6">
-        <v>233160.65</v>
+        <v>315205.10</v>
       </c>
       <c r="J159" s="6">
         <v>0</v>
@@ -6517,31 +6711,31 @@
     </row>
     <row r="160" spans="1:10">
       <c r="A160" s="4" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C160" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D160" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E160" s="6">
-        <v>653586.79</v>
+        <v>315205.10</v>
       </c>
       <c r="F160" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G160" s="6">
-        <v>653586.79</v>
+        <v>315205.10</v>
       </c>
       <c r="H160" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I160" s="6">
-        <v>653586.79</v>
+        <v>315205.10</v>
       </c>
       <c r="J160" s="6">
         <v>0</v>
@@ -6549,31 +6743,31 @@
     </row>
     <row r="161" spans="1:10">
       <c r="A161" s="4" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C161" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D161" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E161" s="6">
-        <v>27692.69</v>
+        <v>315205.10</v>
       </c>
       <c r="F161" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G161" s="6">
-        <v>27692.69</v>
+        <v>315205.10</v>
       </c>
       <c r="H161" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I161" s="6">
-        <v>27692.69</v>
+        <v>315205.10</v>
       </c>
       <c r="J161" s="6">
         <v>0</v>
@@ -6581,31 +6775,31 @@
     </row>
     <row r="162" spans="1:10">
       <c r="A162" s="4" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C162" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D162" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E162" s="6">
-        <v>27692.69</v>
+        <v>315205.10</v>
       </c>
       <c r="F162" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G162" s="6">
-        <v>27692.69</v>
+        <v>315205.10</v>
       </c>
       <c r="H162" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I162" s="6">
-        <v>27692.69</v>
+        <v>315205.10</v>
       </c>
       <c r="J162" s="6">
         <v>0</v>
@@ -6613,31 +6807,31 @@
     </row>
     <row r="163" spans="1:10">
       <c r="A163" s="4" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C163" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D163" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E163" s="6">
-        <v>625894.1</v>
+        <v>5925323.15</v>
       </c>
       <c r="F163" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G163" s="6">
-        <v>625894.1</v>
+        <v>5925323.15</v>
       </c>
       <c r="H163" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I163" s="6">
-        <v>625894.1</v>
+        <v>5925323.15</v>
       </c>
       <c r="J163" s="6">
         <v>0</v>
@@ -6645,31 +6839,31 @@
     </row>
     <row r="164" spans="1:10">
       <c r="A164" s="4" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C164" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D164" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E164" s="6">
-        <v>3732</v>
+        <v>4742034.67</v>
       </c>
       <c r="F164" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G164" s="6">
-        <v>3732</v>
+        <v>4742034.67</v>
       </c>
       <c r="H164" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I164" s="6">
-        <v>3732</v>
+        <v>4742034.67</v>
       </c>
       <c r="J164" s="6">
         <v>0</v>
@@ -6677,31 +6871,31 @@
     </row>
     <row r="165" spans="1:10">
       <c r="A165" s="4" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C165" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D165" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E165" s="6">
-        <v>262494.13</v>
+        <v>840840.60</v>
       </c>
       <c r="F165" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G165" s="6">
-        <v>262494.13</v>
+        <v>840840.60</v>
       </c>
       <c r="H165" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I165" s="6">
-        <v>262494.13</v>
+        <v>840840.60</v>
       </c>
       <c r="J165" s="6">
         <v>0</v>
@@ -6709,31 +6903,31 @@
     </row>
     <row r="166" spans="1:10">
       <c r="A166" s="4" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C166" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D166" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E166" s="6">
-        <v>60921.18</v>
+        <v>252111.54</v>
       </c>
       <c r="F166" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G166" s="6">
-        <v>60921.18</v>
+        <v>252111.54</v>
       </c>
       <c r="H166" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I166" s="6">
-        <v>60921.18</v>
+        <v>252111.54</v>
       </c>
       <c r="J166" s="6">
         <v>0</v>
@@ -6741,31 +6935,31 @@
     </row>
     <row r="167" spans="1:10">
       <c r="A167" s="4" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="C167" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D167" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E167" s="6">
-        <v>298746.79</v>
+        <v>252111.54</v>
       </c>
       <c r="F167" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G167" s="6">
-        <v>298746.79</v>
+        <v>252111.54</v>
       </c>
       <c r="H167" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I167" s="6">
-        <v>298746.79</v>
+        <v>252111.54</v>
       </c>
       <c r="J167" s="6">
         <v>0</v>
@@ -6773,31 +6967,31 @@
     </row>
     <row r="168" spans="1:10">
       <c r="A168" s="4" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C168" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D168" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E168" s="6">
-        <v>117831.83</v>
+        <v>588729.06</v>
       </c>
       <c r="F168" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G168" s="6">
-        <v>117831.83</v>
+        <v>588729.06</v>
       </c>
       <c r="H168" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I168" s="6">
-        <v>117831.83</v>
+        <v>588729.06</v>
       </c>
       <c r="J168" s="6">
         <v>0</v>
@@ -6805,31 +6999,31 @@
     </row>
     <row r="169" spans="1:10">
       <c r="A169" s="4" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C169" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D169" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E169" s="6">
-        <v>117831.83</v>
+        <v>588729.06</v>
       </c>
       <c r="F169" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G169" s="6">
-        <v>117831.83</v>
+        <v>588729.06</v>
       </c>
       <c r="H169" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I169" s="6">
-        <v>117831.83</v>
+        <v>588729.06</v>
       </c>
       <c r="J169" s="6">
         <v>0</v>
@@ -6837,31 +7031,31 @@
     </row>
     <row r="170" spans="1:10">
       <c r="A170" s="4" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C170" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D170" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E170" s="6">
-        <v>52564.29</v>
+        <v>2592610.84</v>
       </c>
       <c r="F170" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G170" s="6">
-        <v>52564.29</v>
+        <v>2592610.84</v>
       </c>
       <c r="H170" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I170" s="6">
-        <v>52564.29</v>
+        <v>2592610.84</v>
       </c>
       <c r="J170" s="6">
         <v>0</v>
@@ -6869,31 +7063,31 @@
     </row>
     <row r="171" spans="1:10">
       <c r="A171" s="4" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C171" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D171" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E171" s="6">
-        <v>17694</v>
+        <v>65287.53</v>
       </c>
       <c r="F171" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G171" s="6">
-        <v>17694</v>
+        <v>65287.53</v>
       </c>
       <c r="H171" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I171" s="6">
-        <v>17694</v>
+        <v>65287.53</v>
       </c>
       <c r="J171" s="6">
         <v>0</v>
@@ -6901,31 +7095,31 @@
     </row>
     <row r="172" spans="1:10">
       <c r="A172" s="4" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C172" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D172" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E172" s="6">
-        <v>47573.54</v>
+        <v>65287.53</v>
       </c>
       <c r="F172" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G172" s="6">
-        <v>47573.54</v>
+        <v>65287.53</v>
       </c>
       <c r="H172" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I172" s="6">
-        <v>47573.54</v>
+        <v>65287.53</v>
       </c>
       <c r="J172" s="6">
         <v>0</v>
@@ -6933,31 +7127,31 @@
     </row>
     <row r="173" spans="1:10">
       <c r="A173" s="4" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C173" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D173" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E173" s="6">
-        <v>8772.84</v>
+        <v>2527323.31</v>
       </c>
       <c r="F173" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G173" s="6">
-        <v>8772.84</v>
+        <v>2527323.31</v>
       </c>
       <c r="H173" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I173" s="6">
-        <v>8772.84</v>
+        <v>2527323.31</v>
       </c>
       <c r="J173" s="6">
         <v>0</v>
@@ -6965,31 +7159,31 @@
     </row>
     <row r="174" spans="1:10">
       <c r="A174" s="4" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="C174" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D174" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E174" s="6">
-        <v>8772.84</v>
+        <v>8708.00</v>
       </c>
       <c r="F174" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G174" s="6">
-        <v>8772.84</v>
+        <v>8708.00</v>
       </c>
       <c r="H174" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I174" s="6">
-        <v>8772.84</v>
+        <v>8708.00</v>
       </c>
       <c r="J174" s="6">
         <v>0</v>
@@ -6997,31 +7191,31 @@
     </row>
     <row r="175" spans="1:10">
       <c r="A175" s="4" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="C175" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D175" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E175" s="6">
-        <v>8772.84</v>
+        <v>983570.88</v>
       </c>
       <c r="F175" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G175" s="6">
-        <v>8772.84</v>
+        <v>983570.88</v>
       </c>
       <c r="H175" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I175" s="6">
-        <v>8772.84</v>
+        <v>983570.88</v>
       </c>
       <c r="J175" s="6">
         <v>0</v>
@@ -7029,31 +7223,31 @@
     </row>
     <row r="176" spans="1:10">
       <c r="A176" s="4" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C176" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D176" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E176" s="6">
-        <v>278460</v>
+        <v>156326.03</v>
       </c>
       <c r="F176" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G176" s="6">
-        <v>278460</v>
+        <v>156326.03</v>
       </c>
       <c r="H176" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I176" s="6">
-        <v>278460</v>
+        <v>156326.03</v>
       </c>
       <c r="J176" s="6">
         <v>0</v>
@@ -7061,31 +7255,31 @@
     </row>
     <row r="177" spans="1:10">
       <c r="A177" s="4" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="C177" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D177" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E177" s="6">
-        <v>278460</v>
+        <v>1378718.40</v>
       </c>
       <c r="F177" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G177" s="6">
-        <v>278460</v>
+        <v>1378718.40</v>
       </c>
       <c r="H177" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I177" s="6">
-        <v>278460</v>
+        <v>1378718.40</v>
       </c>
       <c r="J177" s="6">
         <v>0</v>
@@ -7093,31 +7287,31 @@
     </row>
     <row r="178" spans="1:10">
       <c r="A178" s="4" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C178" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D178" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E178" s="6">
-        <v>278460</v>
+        <v>322300.24</v>
       </c>
       <c r="F178" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G178" s="6">
-        <v>278460</v>
+        <v>322300.24</v>
       </c>
       <c r="H178" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I178" s="6">
-        <v>278460</v>
+        <v>322300.24</v>
       </c>
       <c r="J178" s="6">
         <v>0</v>
@@ -7125,31 +7319,31 @@
     </row>
     <row r="179" spans="1:10">
       <c r="A179" s="4" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C179" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D179" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E179" s="6">
-        <v>1454.22</v>
+        <v>320800.24</v>
       </c>
       <c r="F179" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G179" s="6">
-        <v>1454.22</v>
+        <v>320800.24</v>
       </c>
       <c r="H179" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I179" s="6">
-        <v>1454.22</v>
+        <v>320800.24</v>
       </c>
       <c r="J179" s="6">
         <v>0</v>
@@ -7157,31 +7351,31 @@
     </row>
     <row r="180" spans="1:10">
       <c r="A180" s="4" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C180" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D180" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E180" s="6">
-        <v>1454.22</v>
+        <v>112531.99</v>
       </c>
       <c r="F180" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G180" s="6">
-        <v>1454.22</v>
+        <v>112531.99</v>
       </c>
       <c r="H180" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I180" s="6">
-        <v>1454.22</v>
+        <v>112531.99</v>
       </c>
       <c r="J180" s="6">
         <v>0</v>
@@ -7189,31 +7383,31 @@
     </row>
     <row r="181" spans="1:10">
       <c r="A181" s="4" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C181" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D181" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E181" s="6">
-        <v>1454.22</v>
+        <v>41286.00</v>
       </c>
       <c r="F181" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G181" s="6">
-        <v>1454.22</v>
+        <v>41286.00</v>
       </c>
       <c r="H181" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I181" s="6">
-        <v>1454.22</v>
+        <v>41286.00</v>
       </c>
       <c r="J181" s="6">
         <v>0</v>
@@ -7221,31 +7415,31 @@
     </row>
     <row r="182" spans="1:10">
       <c r="A182" s="4" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C182" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D182" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E182" s="6">
-        <v>52135.74</v>
+        <v>166982.25</v>
       </c>
       <c r="F182" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G182" s="6">
-        <v>52135.74</v>
+        <v>166982.25</v>
       </c>
       <c r="H182" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I182" s="6">
-        <v>52135.74</v>
+        <v>166982.25</v>
       </c>
       <c r="J182" s="6">
         <v>0</v>
@@ -7253,31 +7447,31 @@
     </row>
     <row r="183" spans="1:10">
       <c r="A183" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C183" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D183" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E183" s="6">
-        <v>42415.74</v>
+        <v>1500.00</v>
       </c>
       <c r="F183" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G183" s="6">
-        <v>42415.74</v>
+        <v>1500.00</v>
       </c>
       <c r="H183" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I183" s="6">
-        <v>42415.74</v>
+        <v>1500.00</v>
       </c>
       <c r="J183" s="6">
         <v>0</v>
@@ -7285,31 +7479,31 @@
     </row>
     <row r="184" spans="1:10">
       <c r="A184" s="4" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C184" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D184" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E184" s="6">
-        <v>42415.74</v>
+        <v>1500.00</v>
       </c>
       <c r="F184" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G184" s="6">
-        <v>42415.74</v>
+        <v>1500.00</v>
       </c>
       <c r="H184" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I184" s="6">
-        <v>42415.74</v>
+        <v>1500.00</v>
       </c>
       <c r="J184" s="6">
         <v>0</v>
@@ -7317,31 +7511,31 @@
     </row>
     <row r="185" spans="1:10">
       <c r="A185" s="4" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C185" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D185" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E185" s="6">
-        <v>42415.74</v>
+        <v>66634.57</v>
       </c>
       <c r="F185" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G185" s="6">
-        <v>42415.74</v>
+        <v>66634.57</v>
       </c>
       <c r="H185" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I185" s="6">
-        <v>42415.74</v>
+        <v>66634.57</v>
       </c>
       <c r="J185" s="6">
         <v>0</v>
@@ -7349,31 +7543,31 @@
     </row>
     <row r="186" spans="1:10">
       <c r="A186" s="4" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C186" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D186" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E186" s="6">
-        <v>9720</v>
+        <v>14275.90</v>
       </c>
       <c r="F186" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G186" s="6">
-        <v>9720</v>
+        <v>14275.90</v>
       </c>
       <c r="H186" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I186" s="6">
-        <v>9720</v>
+        <v>14275.90</v>
       </c>
       <c r="J186" s="6">
         <v>0</v>
@@ -7381,31 +7575,31 @@
     </row>
     <row r="187" spans="1:10">
       <c r="A187" s="4" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C187" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D187" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E187" s="6">
-        <v>9720</v>
+        <v>14275.90</v>
       </c>
       <c r="F187" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G187" s="6">
-        <v>9720</v>
+        <v>14275.90</v>
       </c>
       <c r="H187" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I187" s="6">
-        <v>9720</v>
+        <v>14275.90</v>
       </c>
       <c r="J187" s="6">
         <v>0</v>
@@ -7413,31 +7607,31 @@
     </row>
     <row r="188" spans="1:10">
       <c r="A188" s="4" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C188" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D188" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E188" s="6">
-        <v>9720</v>
+        <v>52358.67</v>
       </c>
       <c r="F188" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G188" s="6">
-        <v>9720</v>
+        <v>52358.67</v>
       </c>
       <c r="H188" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I188" s="6">
-        <v>9720</v>
+        <v>52358.67</v>
       </c>
       <c r="J188" s="6">
         <v>0</v>
@@ -7445,31 +7639,31 @@
     </row>
     <row r="189" spans="1:10">
       <c r="A189" s="4" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C189" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D189" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E189" s="6">
-        <v>50486.76</v>
+        <v>18269.55</v>
       </c>
       <c r="F189" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G189" s="6">
-        <v>50486.76</v>
+        <v>18269.55</v>
       </c>
       <c r="H189" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I189" s="6">
-        <v>50486.76</v>
+        <v>18269.55</v>
       </c>
       <c r="J189" s="6">
         <v>0</v>
@@ -7477,31 +7671,31 @@
     </row>
     <row r="190" spans="1:10">
       <c r="A190" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C190" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D190" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E190" s="6">
-        <v>50486.76</v>
+        <v>34089.12</v>
       </c>
       <c r="F190" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G190" s="6">
-        <v>50486.76</v>
+        <v>34089.12</v>
       </c>
       <c r="H190" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I190" s="6">
-        <v>50486.76</v>
+        <v>34089.12</v>
       </c>
       <c r="J190" s="6">
         <v>0</v>
@@ -7509,31 +7703,31 @@
     </row>
     <row r="191" spans="1:10">
       <c r="A191" s="4" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C191" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D191" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E191" s="6">
-        <v>50486.76</v>
+        <v>915687.82</v>
       </c>
       <c r="F191" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G191" s="6">
-        <v>50486.76</v>
+        <v>915687.82</v>
       </c>
       <c r="H191" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I191" s="6">
-        <v>50486.76</v>
+        <v>915687.82</v>
       </c>
       <c r="J191" s="6">
         <v>0</v>
@@ -7541,31 +7735,31 @@
     </row>
     <row r="192" spans="1:10">
       <c r="A192" s="4" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C192" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D192" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E192" s="6">
-        <v>41398.96</v>
+        <v>265947.82</v>
       </c>
       <c r="F192" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G192" s="6">
-        <v>41398.96</v>
+        <v>265947.82</v>
       </c>
       <c r="H192" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I192" s="6">
-        <v>41398.96</v>
+        <v>265947.82</v>
       </c>
       <c r="J192" s="6">
         <v>0</v>
@@ -7573,31 +7767,31 @@
     </row>
     <row r="193" spans="1:10">
       <c r="A193" s="4" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C193" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D193" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E193" s="6">
-        <v>9087.799999999999</v>
+        <v>265947.82</v>
       </c>
       <c r="F193" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G193" s="6">
-        <v>9087.799999999999</v>
+        <v>265947.82</v>
       </c>
       <c r="H193" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I193" s="6">
-        <v>9087.799999999999</v>
+        <v>265947.82</v>
       </c>
       <c r="J193" s="6">
         <v>0</v>
@@ -7605,31 +7799,31 @@
     </row>
     <row r="194" spans="1:10">
       <c r="A194" s="4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C194" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D194" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E194" s="6">
-        <v>166086</v>
+        <v>649740.00</v>
       </c>
       <c r="F194" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G194" s="6">
-        <v>166086</v>
+        <v>649740.00</v>
       </c>
       <c r="H194" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I194" s="6">
-        <v>166086</v>
+        <v>649740.00</v>
       </c>
       <c r="J194" s="6">
         <v>0</v>
@@ -7637,31 +7831,31 @@
     </row>
     <row r="195" spans="1:10">
       <c r="A195" s="4" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C195" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D195" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E195" s="6">
-        <v>161586</v>
+        <v>649740.00</v>
       </c>
       <c r="F195" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G195" s="6">
-        <v>161586</v>
+        <v>649740.00</v>
       </c>
       <c r="H195" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I195" s="6">
-        <v>161586</v>
+        <v>649740.00</v>
       </c>
       <c r="J195" s="6">
         <v>0</v>
@@ -7669,31 +7863,31 @@
     </row>
     <row r="196" spans="1:10">
       <c r="A196" s="4" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C196" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D196" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E196" s="6">
-        <v>161586</v>
+        <v>3960.60</v>
       </c>
       <c r="F196" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G196" s="6">
-        <v>161586</v>
+        <v>3960.60</v>
       </c>
       <c r="H196" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I196" s="6">
-        <v>161586</v>
+        <v>3960.60</v>
       </c>
       <c r="J196" s="6">
         <v>0</v>
@@ -7701,31 +7895,31 @@
     </row>
     <row r="197" spans="1:10">
       <c r="A197" s="4" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C197" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D197" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E197" s="6">
-        <v>161586</v>
+        <v>3960.60</v>
       </c>
       <c r="F197" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G197" s="6">
-        <v>161586</v>
+        <v>3960.60</v>
       </c>
       <c r="H197" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I197" s="6">
-        <v>161586</v>
+        <v>3960.60</v>
       </c>
       <c r="J197" s="6">
         <v>0</v>
@@ -7733,31 +7927,31 @@
     </row>
     <row r="198" spans="1:10">
       <c r="A198" s="4" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C198" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D198" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E198" s="6">
-        <v>4500</v>
+        <v>3960.60</v>
       </c>
       <c r="F198" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G198" s="6">
-        <v>4500</v>
+        <v>3960.60</v>
       </c>
       <c r="H198" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I198" s="6">
-        <v>4500</v>
+        <v>3960.60</v>
       </c>
       <c r="J198" s="6">
         <v>0</v>
@@ -7765,31 +7959,31 @@
     </row>
     <row r="199" spans="1:10">
       <c r="A199" s="4" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C199" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D199" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E199" s="6">
-        <v>4500</v>
+        <v>628774.80</v>
       </c>
       <c r="F199" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G199" s="6">
-        <v>4500</v>
+        <v>628774.80</v>
       </c>
       <c r="H199" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I199" s="6">
-        <v>4500</v>
+        <v>628774.80</v>
       </c>
       <c r="J199" s="6">
         <v>0</v>
@@ -7797,31 +7991,31 @@
     </row>
     <row r="200" spans="1:10">
       <c r="A200" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C200" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D200" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E200" s="6">
-        <v>4500</v>
+        <v>516000.00</v>
       </c>
       <c r="F200" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="G200" s="6">
-        <v>4500</v>
+        <v>516000.00</v>
       </c>
       <c r="H200" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="I200" s="6">
-        <v>4500</v>
+        <v>516000.00</v>
       </c>
       <c r="J200" s="6">
         <v>0</v>
@@ -7829,194 +8023,1410 @@
     </row>
     <row r="201" spans="1:10">
       <c r="A201" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C201" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D201" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E201" s="6">
-        <v>0</v>
+        <v>516000.00</v>
       </c>
       <c r="F201" s="6">
-        <v>7042709.12</v>
+        <v>0.00</v>
       </c>
       <c r="G201" s="6">
-        <v>0</v>
+        <v>516000.00</v>
       </c>
       <c r="H201" s="6">
-        <v>7042709.12</v>
+        <v>0.00</v>
       </c>
       <c r="I201" s="6">
-        <v>0</v>
+        <v>516000.00</v>
       </c>
       <c r="J201" s="6">
-        <v>7042709.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:10">
       <c r="A202" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C202" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D202" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E202" s="6">
-        <v>0</v>
+        <v>516000.00</v>
       </c>
       <c r="F202" s="6">
-        <v>7042709.12</v>
+        <v>0.00</v>
       </c>
       <c r="G202" s="6">
-        <v>0</v>
+        <v>516000.00</v>
       </c>
       <c r="H202" s="6">
-        <v>7042709.12</v>
+        <v>0.00</v>
       </c>
       <c r="I202" s="6">
-        <v>0</v>
+        <v>516000.00</v>
       </c>
       <c r="J202" s="6">
-        <v>7042709.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:10">
       <c r="A203" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B203" s="5" t="s">
         <v>351</v>
       </c>
       <c r="C203" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D203" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E203" s="6">
-        <v>0</v>
+        <v>58537.80</v>
       </c>
       <c r="F203" s="6">
-        <v>7042709.12</v>
+        <v>0.00</v>
       </c>
       <c r="G203" s="6">
-        <v>0</v>
+        <v>58537.80</v>
       </c>
       <c r="H203" s="6">
-        <v>7042709.12</v>
+        <v>0.00</v>
       </c>
       <c r="I203" s="6">
-        <v>0</v>
+        <v>58537.80</v>
       </c>
       <c r="J203" s="6">
-        <v>7042709.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:10">
       <c r="A204" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="B204" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="B204" s="5" t="s">
-        <v>354</v>
-      </c>
       <c r="C204" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D204" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E204" s="6">
-        <v>0</v>
+        <v>58537.80</v>
       </c>
       <c r="F204" s="6">
-        <v>7042709.12</v>
+        <v>0.00</v>
       </c>
       <c r="G204" s="6">
-        <v>0</v>
+        <v>58537.80</v>
       </c>
       <c r="H204" s="6">
-        <v>7042709.12</v>
+        <v>0.00</v>
       </c>
       <c r="I204" s="6">
-        <v>0</v>
+        <v>58537.80</v>
       </c>
       <c r="J204" s="6">
-        <v>7042709.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:10">
       <c r="A205" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C205" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="D205" s="6">
-        <v>0</v>
+        <v>0.00</v>
       </c>
       <c r="E205" s="6">
-        <v>0</v>
+        <v>58537.80</v>
       </c>
       <c r="F205" s="6">
-        <v>7042709.12</v>
+        <v>0.00</v>
       </c>
       <c r="G205" s="6">
-        <v>0</v>
+        <v>58537.80</v>
       </c>
       <c r="H205" s="6">
-        <v>7042709.12</v>
+        <v>0.00</v>
       </c>
       <c r="I205" s="6">
-        <v>0</v>
+        <v>58537.80</v>
       </c>
       <c r="J205" s="6">
-        <v>7042709.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:10">
       <c r="A206" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B206" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="B206" s="5" t="s">
+      <c r="C206" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D206" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E206" s="6">
+        <v>54237.00</v>
+      </c>
+      <c r="F206" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G206" s="6">
+        <v>54237.00</v>
+      </c>
+      <c r="H206" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I206" s="6">
+        <v>54237.00</v>
+      </c>
+      <c r="J206" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10">
+      <c r="A207" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="C206" s="6">
-        <v>0</v>
-      </c>
-      <c r="D206" s="6">
-        <v>0</v>
-      </c>
-      <c r="E206" s="6">
-        <v>0</v>
-      </c>
-      <c r="F206" s="6">
-        <v>7042709.12</v>
-      </c>
-      <c r="G206" s="6">
-        <v>0</v>
-      </c>
-      <c r="H206" s="6">
-        <v>7042709.12</v>
-      </c>
-      <c r="I206" s="6">
-        <v>0</v>
-      </c>
-      <c r="J206" s="6">
-        <v>7042709.12</v>
+      <c r="B207" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="C207" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D207" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E207" s="6">
+        <v>54237.00</v>
+      </c>
+      <c r="F207" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G207" s="6">
+        <v>54237.00</v>
+      </c>
+      <c r="H207" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I207" s="6">
+        <v>54237.00</v>
+      </c>
+      <c r="J207" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10">
+      <c r="A208" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="C208" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D208" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E208" s="6">
+        <v>54237.00</v>
+      </c>
+      <c r="F208" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G208" s="6">
+        <v>54237.00</v>
+      </c>
+      <c r="H208" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I208" s="6">
+        <v>54237.00</v>
+      </c>
+      <c r="J208" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10">
+      <c r="A209" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C209" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D209" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E209" s="6">
+        <v>81525.68</v>
+      </c>
+      <c r="F209" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G209" s="6">
+        <v>81525.68</v>
+      </c>
+      <c r="H209" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I209" s="6">
+        <v>81525.68</v>
+      </c>
+      <c r="J209" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10">
+      <c r="A210" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="C210" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D210" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E210" s="6">
+        <v>11445.68</v>
+      </c>
+      <c r="F210" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G210" s="6">
+        <v>11445.68</v>
+      </c>
+      <c r="H210" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I210" s="6">
+        <v>11445.68</v>
+      </c>
+      <c r="J210" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10">
+      <c r="A211" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C211" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D211" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E211" s="6">
+        <v>11445.68</v>
+      </c>
+      <c r="F211" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G211" s="6">
+        <v>11445.68</v>
+      </c>
+      <c r="H211" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I211" s="6">
+        <v>11445.68</v>
+      </c>
+      <c r="J211" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10">
+      <c r="A212" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="C212" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D212" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E212" s="6">
+        <v>8689.64</v>
+      </c>
+      <c r="F212" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G212" s="6">
+        <v>8689.64</v>
+      </c>
+      <c r="H212" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I212" s="6">
+        <v>8689.64</v>
+      </c>
+      <c r="J212" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10">
+      <c r="A213" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C213" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D213" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E213" s="6">
+        <v>2756.04</v>
+      </c>
+      <c r="F213" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G213" s="6">
+        <v>2756.04</v>
+      </c>
+      <c r="H213" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I213" s="6">
+        <v>2756.04</v>
+      </c>
+      <c r="J213" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10">
+      <c r="A214" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="C214" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D214" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E214" s="6">
+        <v>70080.00</v>
+      </c>
+      <c r="F214" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G214" s="6">
+        <v>70080.00</v>
+      </c>
+      <c r="H214" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I214" s="6">
+        <v>70080.00</v>
+      </c>
+      <c r="J214" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10">
+      <c r="A215" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="C215" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D215" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E215" s="6">
+        <v>70080.00</v>
+      </c>
+      <c r="F215" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G215" s="6">
+        <v>70080.00</v>
+      </c>
+      <c r="H215" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I215" s="6">
+        <v>70080.00</v>
+      </c>
+      <c r="J215" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10">
+      <c r="A216" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C216" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D216" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E216" s="6">
+        <v>62400.00</v>
+      </c>
+      <c r="F216" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G216" s="6">
+        <v>62400.00</v>
+      </c>
+      <c r="H216" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I216" s="6">
+        <v>62400.00</v>
+      </c>
+      <c r="J216" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10">
+      <c r="A217" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C217" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D217" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E217" s="6">
+        <v>7680.00</v>
+      </c>
+      <c r="F217" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G217" s="6">
+        <v>7680.00</v>
+      </c>
+      <c r="H217" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I217" s="6">
+        <v>7680.00</v>
+      </c>
+      <c r="J217" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10">
+      <c r="A218" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C218" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D218" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E218" s="6">
+        <v>472988.00</v>
+      </c>
+      <c r="F218" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G218" s="6">
+        <v>472988.00</v>
+      </c>
+      <c r="H218" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I218" s="6">
+        <v>472988.00</v>
+      </c>
+      <c r="J218" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10">
+      <c r="A219" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C219" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D219" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E219" s="6">
+        <v>226188.00</v>
+      </c>
+      <c r="F219" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G219" s="6">
+        <v>226188.00</v>
+      </c>
+      <c r="H219" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I219" s="6">
+        <v>226188.00</v>
+      </c>
+      <c r="J219" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10">
+      <c r="A220" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C220" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D220" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E220" s="6">
+        <v>226188.00</v>
+      </c>
+      <c r="F220" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G220" s="6">
+        <v>226188.00</v>
+      </c>
+      <c r="H220" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I220" s="6">
+        <v>226188.00</v>
+      </c>
+      <c r="J220" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10">
+      <c r="A221" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C221" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D221" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E221" s="6">
+        <v>226188.00</v>
+      </c>
+      <c r="F221" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G221" s="6">
+        <v>226188.00</v>
+      </c>
+      <c r="H221" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I221" s="6">
+        <v>226188.00</v>
+      </c>
+      <c r="J221" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10">
+      <c r="A222" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="C222" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D222" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E222" s="6">
+        <v>57000.00</v>
+      </c>
+      <c r="F222" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G222" s="6">
+        <v>57000.00</v>
+      </c>
+      <c r="H222" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I222" s="6">
+        <v>57000.00</v>
+      </c>
+      <c r="J222" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10">
+      <c r="A223" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="C223" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D223" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E223" s="6">
+        <v>57000.00</v>
+      </c>
+      <c r="F223" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G223" s="6">
+        <v>57000.00</v>
+      </c>
+      <c r="H223" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I223" s="6">
+        <v>57000.00</v>
+      </c>
+      <c r="J223" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10">
+      <c r="A224" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C224" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D224" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E224" s="6">
+        <v>57000.00</v>
+      </c>
+      <c r="F224" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G224" s="6">
+        <v>57000.00</v>
+      </c>
+      <c r="H224" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I224" s="6">
+        <v>57000.00</v>
+      </c>
+      <c r="J224" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10">
+      <c r="A225" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="C225" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D225" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E225" s="6">
+        <v>140000.00</v>
+      </c>
+      <c r="F225" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G225" s="6">
+        <v>140000.00</v>
+      </c>
+      <c r="H225" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I225" s="6">
+        <v>140000.00</v>
+      </c>
+      <c r="J225" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10">
+      <c r="A226" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="C226" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D226" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E226" s="6">
+        <v>140000.00</v>
+      </c>
+      <c r="F226" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G226" s="6">
+        <v>140000.00</v>
+      </c>
+      <c r="H226" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I226" s="6">
+        <v>140000.00</v>
+      </c>
+      <c r="J226" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10">
+      <c r="A227" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="C227" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D227" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E227" s="6">
+        <v>140000.00</v>
+      </c>
+      <c r="F227" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G227" s="6">
+        <v>140000.00</v>
+      </c>
+      <c r="H227" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I227" s="6">
+        <v>140000.00</v>
+      </c>
+      <c r="J227" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10">
+      <c r="A228" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="C228" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D228" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E228" s="6">
+        <v>49800.00</v>
+      </c>
+      <c r="F228" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G228" s="6">
+        <v>49800.00</v>
+      </c>
+      <c r="H228" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I228" s="6">
+        <v>49800.00</v>
+      </c>
+      <c r="J228" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10">
+      <c r="A229" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="C229" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D229" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E229" s="6">
+        <v>49800.00</v>
+      </c>
+      <c r="F229" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G229" s="6">
+        <v>49800.00</v>
+      </c>
+      <c r="H229" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I229" s="6">
+        <v>49800.00</v>
+      </c>
+      <c r="J229" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10">
+      <c r="A230" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="C230" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D230" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E230" s="6">
+        <v>49800.00</v>
+      </c>
+      <c r="F230" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G230" s="6">
+        <v>49800.00</v>
+      </c>
+      <c r="H230" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I230" s="6">
+        <v>49800.00</v>
+      </c>
+      <c r="J230" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10">
+      <c r="A231" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="C231" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D231" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E231" s="6">
+        <v>89778.20</v>
+      </c>
+      <c r="F231" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G231" s="6">
+        <v>89778.20</v>
+      </c>
+      <c r="H231" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I231" s="6">
+        <v>89778.20</v>
+      </c>
+      <c r="J231" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10">
+      <c r="A232" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="C232" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D232" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E232" s="6">
+        <v>89778.20</v>
+      </c>
+      <c r="F232" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G232" s="6">
+        <v>89778.20</v>
+      </c>
+      <c r="H232" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I232" s="6">
+        <v>89778.20</v>
+      </c>
+      <c r="J232" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10">
+      <c r="A233" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C233" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D233" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E233" s="6">
+        <v>89778.20</v>
+      </c>
+      <c r="F233" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G233" s="6">
+        <v>89778.20</v>
+      </c>
+      <c r="H233" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I233" s="6">
+        <v>89778.20</v>
+      </c>
+      <c r="J233" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10">
+      <c r="A234" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C234" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D234" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E234" s="6">
+        <v>89778.20</v>
+      </c>
+      <c r="F234" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G234" s="6">
+        <v>89778.20</v>
+      </c>
+      <c r="H234" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I234" s="6">
+        <v>89778.20</v>
+      </c>
+      <c r="J234" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10">
+      <c r="A235" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="C235" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D235" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E235" s="6">
+        <v>39799.20</v>
+      </c>
+      <c r="F235" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G235" s="6">
+        <v>39799.20</v>
+      </c>
+      <c r="H235" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I235" s="6">
+        <v>39799.20</v>
+      </c>
+      <c r="J235" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10">
+      <c r="A236" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C236" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D236" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E236" s="6">
+        <v>39799.20</v>
+      </c>
+      <c r="F236" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G236" s="6">
+        <v>39799.20</v>
+      </c>
+      <c r="H236" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I236" s="6">
+        <v>39799.20</v>
+      </c>
+      <c r="J236" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10">
+      <c r="A237" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C237" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D237" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E237" s="6">
+        <v>49979.00</v>
+      </c>
+      <c r="F237" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G237" s="6">
+        <v>49979.00</v>
+      </c>
+      <c r="H237" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I237" s="6">
+        <v>49979.00</v>
+      </c>
+      <c r="J237" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10">
+      <c r="A238" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="C238" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D238" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E238" s="6">
+        <v>49979.00</v>
+      </c>
+      <c r="F238" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="G238" s="6">
+        <v>49979.00</v>
+      </c>
+      <c r="H238" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="I238" s="6">
+        <v>49979.00</v>
+      </c>
+      <c r="J238" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10">
+      <c r="A239" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="C239" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D239" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E239" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="F239" s="6">
+        <v>20501635.05</v>
+      </c>
+      <c r="G239" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="H239" s="6">
+        <v>20501635.05</v>
+      </c>
+      <c r="I239" s="6">
+        <v>0</v>
+      </c>
+      <c r="J239" s="6">
+        <v>20501635.05</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10">
+      <c r="A240" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="C240" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D240" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E240" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="F240" s="6">
+        <v>20501635.05</v>
+      </c>
+      <c r="G240" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="H240" s="6">
+        <v>20501635.05</v>
+      </c>
+      <c r="I240" s="6">
+        <v>0</v>
+      </c>
+      <c r="J240" s="6">
+        <v>20501635.05</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10">
+      <c r="A241" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="C241" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D241" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E241" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="F241" s="6">
+        <v>20501635.05</v>
+      </c>
+      <c r="G241" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="H241" s="6">
+        <v>20501635.05</v>
+      </c>
+      <c r="I241" s="6">
+        <v>0</v>
+      </c>
+      <c r="J241" s="6">
+        <v>20501635.05</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10">
+      <c r="A242" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="C242" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D242" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E242" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="F242" s="6">
+        <v>20501635.05</v>
+      </c>
+      <c r="G242" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="H242" s="6">
+        <v>20501635.05</v>
+      </c>
+      <c r="I242" s="6">
+        <v>0</v>
+      </c>
+      <c r="J242" s="6">
+        <v>20501635.05</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10">
+      <c r="A243" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="C243" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D243" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E243" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="F243" s="6">
+        <v>20501635.05</v>
+      </c>
+      <c r="G243" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="H243" s="6">
+        <v>20501635.05</v>
+      </c>
+      <c r="I243" s="6">
+        <v>0</v>
+      </c>
+      <c r="J243" s="6">
+        <v>20501635.05</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10">
+      <c r="A244" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="C244" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="D244" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E244" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="F244" s="6">
+        <v>20501635.05</v>
+      </c>
+      <c r="G244" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="H244" s="6">
+        <v>20501635.05</v>
+      </c>
+      <c r="I244" s="6">
+        <v>0</v>
+      </c>
+      <c r="J244" s="6">
+        <v>20501635.05</v>
       </c>
     </row>
   </sheetData>
